--- a/correspondance_variables.xlsx
+++ b/correspondance_variables.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F422"/>
+  <dimension ref="A1:F425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OPERATEUR</t>
+          <t>REGION_ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Opérateur</t>
+          <t>Région administrative</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>select_one reseau</t>
+          <t>select_one region</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DATE_INTERVIEW</t>
+          <t>DEPARTEMENT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Département</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one departement</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -589,7 +589,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JOUR_SEMAINE</t>
+          <t>VILLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jour</t>
+          <t>Ville</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one ville</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -617,7 +617,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HEURE_DEBUT</t>
+          <t>OPERATEUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Heure début</t>
+          <t>Opérateur</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one reseau</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LANGUE_ENQ</t>
+          <t>DATE_INTERVIEW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Langue</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>select_one langue</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -671,19 +671,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>IDENT_CONSEILLER</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JOUR_SEMAINE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Identification conseiller</t>
+          <t>Jour</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -699,24 +699,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRANCHE_HORAIRE</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HEURE_DEBUT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tranche horaire</t>
+          <t>Heure début</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>select_one tranche_horaire</t>
+          <t>time</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -727,37 +727,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>T_ATTENTE</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LANGUE_ENQ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Temps d'attente avant conseiller</t>
+          <t>Langue</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one langue</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mesures — valeurs observées</t>
+          <t>Identification de l'enquêteur</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>T_DUREE_APPEL</t>
+          <t>IDENT_CONSEILLER</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -767,53 +767,53 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Durée totale de l'appel</t>
+          <t>Identification conseiller</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mesures — valeurs observées</t>
+          <t>Identification de l'enquêteur</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TEMPS_TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TRANCHE_HORAIRE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Temps total en minutes passé en ligne avec le conseiller</t>
+          <t>Tranche horaire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one tranche_horaire</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mesures — valeurs observées</t>
+          <t>Identification de l'enquêteur</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NB_ATTENTES</t>
+          <t>T_ATTENTE</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nombre de mises en attente</t>
+          <t>Temps d'attente avant conseiller</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T_ATTENTES</t>
+          <t>T_DUREE_APPEL</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durée cumulée des mises en attente</t>
+          <t>Durée totale de l'appel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -867,24 +867,24 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>NB_TRANSFERTS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TEMPS_TOTAL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nombre de transferts</t>
+          <t>Temps total en minutes passé en ligne avec le conseiller</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -897,7 +897,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RENVOI</t>
+          <t>NB_ATTENTES</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Renvoi : le conseiller a-t-il orienté le client ailleurs qu'au téléphone ?</t>
+          <t>Nombre de mises en attente</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>select_one renvoi</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -925,7 +925,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RENVOI_PRECISION</t>
+          <t>T_ATTENTES</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Préciser le canal, l'agence ou le point de vente indiqués</t>
+          <t>Durée cumulée des mises en attente</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -953,7 +953,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ESCALADE</t>
+          <t>NB_TRANSFERTS</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Escalade : le dossier a-t-il été transmis à un autre service ou un rappel a-t-il été promis ?</t>
+          <t>Nombre de transferts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>select_one oui_non</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -979,37 +979,37 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SCENARIO</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RENVOI</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scénario</t>
+          <t>Renvoi : le conseiller a-t-il orienté le client ailleurs qu'au téléphone ?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>select_one scenario</t>
+          <t>select_one renvoi</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Scénario joué</t>
+          <t>Mesures — valeurs observées</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>RENVOI_PRECISION</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1019,29 +1019,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1 Le message d'accueil et les menus du serveur vocal vous ont-ils semblé clairs, compréhensibles et cohérents avec les </t>
+          <t>Préciser le canal, l'agence ou le point de vente indiqués</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>section A</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
+          <t>Mesures — valeurs observées</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Q1_ALERTE</t>
+          <t>ESCALADE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1051,53 +1047,53 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Escalade : le dossier a-t-il été transmis à un autre service ou un rappel a-t-il été promis ?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>select_multiple alertes_a</t>
+          <t>select_one oui_non</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
+          <t>Mesures — valeurs observées</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Q1_COM</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SCENARIO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Scénario</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one scenario</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
+          <t>Scénario joué</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1107,7 +1103,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Q2 Le choix de langue vous a-t-il été proposé et a-t-il fonctionné correctement lorsqu'il était applicable à votre parco</t>
+          <t xml:space="preserve">Q1 Le message d'accueil et les menus du serveur vocal vous ont-ils semblé clairs, compréhensibles et cohérents avec les </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1129,7 +1125,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Q2_ALERTE</t>
+          <t>Q1_ALERTE</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1157,7 +1153,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Q2_COM</t>
+          <t>Q1_COM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1185,7 +1181,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1195,7 +1191,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Q3 L'accès à un conseiller vous a-t-il semblé simple et fluide, sans erreur, ni boucle inutile ni confusion dans le parc</t>
+          <t>Q2 Le choix de langue vous a-t-il été proposé et a-t-il fonctionné correctement lorsqu'il était applicable à votre parco</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1217,7 +1213,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Q3_ALERTE</t>
+          <t>Q2_ALERTE</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1245,7 +1241,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Q3_COM</t>
+          <t>Q2_COM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1273,7 +1269,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SCORE_A</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1283,15 +1279,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Score — Accessibilité &amp; serveur vocal</t>
+          <t>Q3 L'accès à un conseiller vous a-t-il semblé simple et fluide, sans erreur, ni boucle inutile ni confusion dans le parc</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>section A</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
@@ -1301,7 +1301,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3_ALERTE</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1311,29 +1311,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Q4 Le conseiller vous a-t-il accueilli et s'est-il présenté de manière claire et professionnelle ?</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>section B</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_a</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
+          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Q4_ALERTE</t>
+          <t>Q3_COM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1343,25 +1339,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
+          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Q4_COM</t>
+          <t>SCORE_A</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1371,25 +1367,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Accessibilité &amp; serveur vocal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
+          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1399,7 +1395,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Q5 Le ton du conseiller vous a-t-il semblé courtois, agréable et disponible, avec une personnalisation naturelle et appr</t>
+          <t>Q4 Le conseiller vous a-t-il accueilli et s'est-il présenté de manière claire et professionnelle ?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1421,7 +1417,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Q5_ALERTE</t>
+          <t>Q4_ALERTE</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1449,7 +1445,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Q5_COM</t>
+          <t>Q4_COM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1477,7 +1473,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SCORE_B</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1487,15 +1483,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Score — Accueil &amp; posture du conseiller</t>
+          <t>Q5 Le ton du conseiller vous a-t-il semblé courtois, agréable et disponible, avec une personnalisation naturelle et appr</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>section B</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
@@ -1505,7 +1505,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q5_ALERTE</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1515,29 +1515,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Q6 Le conseiller vous a-t-il écouté attentivement et vous a-t-il laissé exposer votre besoin sans interruption inappropr</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>section C</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_nc</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C. COMPRÉHENSION DU BESOIN</t>
+          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Q6_ALERTE</t>
+          <t>Q5_COM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1547,25 +1543,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>select_multiple alertes_c</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C. COMPRÉHENSION DU BESOIN</t>
+          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Q6_COM</t>
+          <t>SCORE_B</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1575,25 +1571,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Accueil &amp; posture du conseiller</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C. COMPRÉHENSION DU BESOIN</t>
+          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1603,7 +1599,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Q7 Le conseiller a-t-il posé des questions pertinentes pour qualifier votre problème et obtenir uniquement les informati</t>
+          <t>Q6 Le conseiller vous a-t-il écouté attentivement et vous a-t-il laissé exposer votre besoin sans interruption inappropr</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1625,7 +1621,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q7_ALERTE</t>
+          <t>Q6_ALERTE</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1653,7 +1649,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q7_COM</t>
+          <t>Q6_COM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1681,7 +1677,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1691,7 +1687,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Q8 Le conseiller a-t-il reformulé ou validé sa compréhension lorsque cela était utile, en évitant que vous répétiez inut</t>
+          <t>Q7 Le conseiller a-t-il posé des questions pertinentes pour qualifier votre problème et obtenir uniquement les informati</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1713,7 +1709,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Q8_ALERTE</t>
+          <t>Q7_ALERTE</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1741,7 +1737,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Q8_COM</t>
+          <t>Q7_COM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1769,7 +1765,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SCORE_C</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1779,15 +1775,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Score — Compréhension du besoin</t>
+          <t>Q8 Le conseiller a-t-il reformulé ou validé sa compréhension lorsque cela était utile, en évitant que vous répétiez inut</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>section C</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>C. COMPRÉHENSION DU BESOIN</t>
@@ -1797,7 +1797,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q8_ALERTE</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1807,29 +1807,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9 Le conseiller a-t-il démontré une bonne maîtrise des offres, services, procédures et parcours liés au scénario testé </t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>section D</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_c</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
+          <t>C. COMPRÉHENSION DU BESOIN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Q9_ALERTE</t>
+          <t>Q8_COM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1839,25 +1835,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>select_multiple alertes_q9</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
+          <t>C. COMPRÉHENSION DU BESOIN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Q9_COM</t>
+          <t>SCORE_C</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1867,25 +1863,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Compréhension du besoin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
+          <t>C. COMPRÉHENSION DU BESOIN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1895,7 +1891,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Q10 La réponse fournie par le conseiller était-elle correcte, précise, cohérente et exempte d'informations contradictoir</t>
+          <t xml:space="preserve">Q9 Le conseiller a-t-il démontré une bonne maîtrise des offres, services, procédures et parcours liés au scénario testé </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1917,7 +1913,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Q10_ALERTE</t>
+          <t>Q9_ALERTE</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1932,7 +1928,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>select_multiple alertes_q10</t>
+          <t>select_multiple alertes_q9</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1945,7 +1941,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Q10_COM</t>
+          <t>Q9_COM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1973,7 +1969,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1983,7 +1979,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Q11 Les explications données vous ont-elles semblé simples, pédagogiques et adaptées, avec des étapes ou alternatives cl</t>
+          <t>Q10 La réponse fournie par le conseiller était-elle correcte, précise, cohérente et exempte d'informations contradictoir</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2005,7 +2001,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Q11_ALERTE</t>
+          <t>Q10_ALERTE</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2020,7 +2016,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>select_multiple alertes_q11</t>
+          <t>select_multiple alertes_q10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2033,7 +2029,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Q11_COM</t>
+          <t>Q10_COM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2061,7 +2057,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SCORE_D</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2071,15 +2067,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Score — Expertise &amp; exactitude de la réponse</t>
+          <t>Q11 Les explications données vous ont-elles semblé simples, pédagogiques et adaptées, avec des étapes ou alternatives cl</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>section D</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
@@ -2089,7 +2089,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q11_ALERTE</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2099,29 +2099,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Q12 La réponse apportée par le conseiller était-elle concrète, exploitable et vous a-t-elle permis d'avancer immédiateme</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>section E</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_q11</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
+          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Q12_ALERTE</t>
+          <t>Q11_COM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2131,25 +2127,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
+          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Q12_COM</t>
+          <t>SCORE_D</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2159,25 +2155,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Expertise &amp; exactitude de la réponse</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
+          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2187,7 +2183,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Q13 Votre besoin a-t-il été résolu dès le premier contact ou, lorsque la résolution immédiate était impossible, la meill</t>
+          <t>Q12 La réponse apportée par le conseiller était-elle concrète, exploitable et vous a-t-elle permis d'avancer immédiateme</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2209,7 +2205,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Q13_ALERTE</t>
+          <t>Q12_ALERTE</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2237,7 +2233,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Q13_COM</t>
+          <t>Q12_COM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2265,7 +2261,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2275,7 +2271,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Q14 Le conseiller a-t-il pris ownership de votre demande, en évitant les transferts, renvois ou abandons de prise en cha</t>
+          <t>Q13 Votre besoin a-t-il été résolu dès le premier contact ou, lorsque la résolution immédiate était impossible, la meill</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2297,7 +2293,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Q14_ALERTE</t>
+          <t>Q13_ALERTE</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2325,7 +2321,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Q14_COM</t>
+          <t>Q13_COM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2353,7 +2349,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2363,7 +2359,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Q15 En cas d'escalade ou de renvoi en agence, le motif, les prochaines étapes, les pièces éventuelles et le délai annonc</t>
+          <t>Q14 Le conseiller a-t-il pris ownership de votre demande, en évitant les transferts, renvois ou abandons de prise en cha</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2385,7 +2381,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Q15_ALERTE</t>
+          <t>Q14_ALERTE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2413,7 +2409,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Q15_COM</t>
+          <t>Q14_COM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2441,7 +2437,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q15</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2451,7 +2447,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Q16 Avant de clôturer l'appel, le conseiller a-t-il vérifié que la solution ou la suite du traitement était bien compris</t>
+          <t>Q15 En cas d'escalade ou de renvoi en agence, le motif, les prochaines étapes, les pièces éventuelles et le délai annonc</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2473,7 +2469,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Q16_ALERTE</t>
+          <t>Q15_ALERTE</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -2501,7 +2497,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Q16_COM</t>
+          <t>Q15_COM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2529,7 +2525,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SCORE_E</t>
+          <t>Q16</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2539,15 +2535,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Score — Résolution / FCR &amp; ownership</t>
+          <t>Q16 Avant de clôturer l'appel, le conseiller a-t-il vérifié que la solution ou la suite du traitement était bien compris</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>section E</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
@@ -2557,7 +2557,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q16_ALERTE</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2567,29 +2567,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Q17 Le nombre d'étapes, d'informations demandées et de manipulations imposées au client vous a-t-il semblé limité au str</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>section F</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_nc</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
+          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q17_ALERTE</t>
+          <t>Q16_COM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -2599,25 +2595,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
+          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Q17_COM</t>
+          <t>SCORE_E</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2627,25 +2623,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Résolution / FCR &amp; ownership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
+          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q17</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -2655,7 +2651,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Q18 Les mises en attente, transferts et changements de canal ont-ils été minimisés et, lorsqu'ils étaient nécessaires, e</t>
+          <t>Q17 Le nombre d'étapes, d'informations demandées et de manipulations imposées au client vous a-t-il semblé limité au str</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2677,7 +2673,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Q18_ALERTE</t>
+          <t>Q17_ALERTE</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2705,7 +2701,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Q18_COM</t>
+          <t>Q17_COM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -2733,7 +2729,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SCORE_F</t>
+          <t>Q18</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2743,15 +2739,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Score — Effort client &amp; simplicité</t>
+          <t>Q18 Les mises en attente, transferts et changements de canal ont-ils été minimisés et, lorsqu'ils étaient nécessaires, e</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>section F</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
@@ -2761,7 +2761,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q18_ALERTE</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -2771,29 +2771,25 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Q19 Le conseiller a-t-il reconnu de façon appropriée l'inconfort, l'urgence ou l'émotion que vous avez exprimés, notamme</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>section G</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_nc</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>G. EMPATHIE &amp; CONFIANCE</t>
+          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Q19_ALERTE</t>
+          <t>Q18_COM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2803,25 +2799,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>G. EMPATHIE &amp; CONFIANCE</t>
+          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Q19_COM</t>
+          <t>SCORE_F</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -2831,25 +2827,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Effort client &amp; simplicité</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>G. EMPATHIE &amp; CONFIANCE</t>
+          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q19</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2859,7 +2855,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Q20 L'attitude du conseiller, la transparence de ses explications et le respect de la confidentialité vous ont-ils inspi</t>
+          <t>Q19 Le conseiller a-t-il reconnu de façon appropriée l'inconfort, l'urgence ou l'émotion que vous avez exprimés, notamme</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2881,7 +2877,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Q20_ALERTE</t>
+          <t>Q19_ALERTE</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -2909,7 +2905,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Q20_COM</t>
+          <t>Q19_COM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2937,7 +2933,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SCORE_G</t>
+          <t>Q20</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -2947,15 +2943,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Score — Empathie &amp; confiance</t>
+          <t>Q20 L'attitude du conseiller, la transparence de ses explications et le respect de la confidentialité vous ont-ils inspi</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>section G</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>G. EMPATHIE &amp; CONFIANCE</t>
@@ -2965,7 +2965,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q20_ALERTE</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2975,29 +2975,25 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Q21 Le conseiller a-t-il récapitulé brièvement la solution ou les prochaines étapes, en vérifiant qu'aucun point essenti</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>section H</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_nc</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>H. CLÔTURE DE L'ENTRETIEN</t>
+          <t>G. EMPATHIE &amp; CONFIANCE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Q21_ALERTE</t>
+          <t>Q20_COM</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -3007,25 +3003,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>H. CLÔTURE DE L'ENTRETIEN</t>
+          <t>G. EMPATHIE &amp; CONFIANCE</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Q21_COM</t>
+          <t>SCORE_G</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3035,25 +3031,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Empathie &amp; confiance</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>H. CLÔTURE DE L'ENTRETIEN</t>
+          <t>G. EMPATHIE &amp; CONFIANCE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q21</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -3063,7 +3059,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Q22 La prise de congé du conseiller vous a-t-elle semblé courtoise, naturelle et professionnelle (remerciement ou souhai</t>
+          <t>Q21 Le conseiller a-t-il récapitulé brièvement la solution ou les prochaines étapes, en vérifiant qu'aucun point essenti</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3085,7 +3081,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Q22_ALERTE</t>
+          <t>Q21_ALERTE</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3113,7 +3109,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Q22_COM</t>
+          <t>Q21_COM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -3141,7 +3137,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q22</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3151,7 +3147,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Q23 Le conseiller a-t-il informé le client qu'il recevra un sondage de satisfaction afin de partager son avis ?</t>
+          <t>Q22 La prise de congé du conseiller vous a-t-elle semblé courtoise, naturelle et professionnelle (remerciement ou souhai</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3173,7 +3169,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Q23_ALERTE</t>
+          <t>Q22_ALERTE</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -3201,7 +3197,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Q23_COM</t>
+          <t>Q22_COM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3229,7 +3225,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SCORE_H</t>
+          <t>Q23</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -3239,15 +3235,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Score — Clôture de l'entretien</t>
+          <t>Q23 Le conseiller a-t-il informé le client qu'il recevra un sondage de satisfaction afin de partager son avis ?</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>section H</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>H. CLÔTURE DE L'ENTRETIEN</t>
@@ -3257,7 +3257,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>S01_1</t>
+          <t>Q23_ALERTE</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3267,29 +3267,25 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>S01_1 Diagnostic — Le conseiller a-t-il identifié clairement la nature du problème et expliqué les causes possibles de l</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>section I</t>
-        </is>
-      </c>
+          <t>select_multiple alertes_nc</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>I. MAÎTRISE DU SCÉNARIO</t>
+          <t>H. CLÔTURE DE L'ENTRETIEN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>S01_1_ALERTE</t>
+          <t>Q23_COM</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -3299,25 +3295,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>I. MAÎTRISE DU SCÉNARIO</t>
+          <t>H. CLÔTURE DE L'ENTRETIEN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>S01_1_COM</t>
+          <t>SCORE_H</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3327,25 +3323,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Score — Clôture de l'entretien</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>I. MAÎTRISE DU SCÉNARIO</t>
+          <t>H. CLÔTURE DE L'ENTRETIEN</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>S01_2</t>
+          <t>S01_1</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -3355,7 +3351,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>S01_2 Qualification — Le conseiller a-t-il posé des questions pertinentes pour qualifier le problème (forfait, téléphone</t>
+          <t>S01_1 Diagnostic — Le conseiller a-t-il identifié clairement la nature du problème et expliqué les causes possibles de l</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3377,7 +3373,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>S01_2_ALERTE</t>
+          <t>S01_1_ALERTE</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -3405,7 +3401,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>S01_2_COM</t>
+          <t>S01_1_COM</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -3433,7 +3429,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>S01_3</t>
+          <t>S01_2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -3443,7 +3439,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>S01_3 Vérification du contexte — Le conseiller a-t-il vérifié votre localisation, le type de terminal ou d'autres élémen</t>
+          <t>S01_2 Qualification — Le conseiller a-t-il posé des questions pertinentes pour qualifier le problème (forfait, téléphone</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3465,7 +3461,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>S01_3_ALERTE</t>
+          <t>S01_2_ALERTE</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -3493,7 +3489,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>S01_3_COM</t>
+          <t>S01_2_COM</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -3521,7 +3517,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>S01_4</t>
+          <t>S01_3</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -3531,7 +3527,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">S01_4 Solution — Le conseiller a-t-il proposé une solution concrète et adaptée pour rétablir la qualité de la connexion </t>
+          <t>S01_3 Vérification du contexte — Le conseiller a-t-il vérifié votre localisation, le type de terminal ou d'autres élémen</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3553,7 +3549,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>S01_4_ALERTE</t>
+          <t>S01_3_ALERTE</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -3581,7 +3577,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>S01_4_COM</t>
+          <t>S01_3_COM</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -3609,7 +3605,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>S01_5</t>
+          <t>S01_4</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -3619,7 +3615,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>S01_5 Pédagogie — Le conseiller a-t-il expliqué les étapes de manière simple et compréhensible, vous permettant de repro</t>
+          <t xml:space="preserve">S01_4 Solution — Le conseiller a-t-il proposé une solution concrète et adaptée pour rétablir la qualité de la connexion </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3641,7 +3637,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>S01_5_ALERTE</t>
+          <t>S01_4_ALERTE</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -3669,7 +3665,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>S01_5_COM</t>
+          <t>S01_4_COM</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -3697,7 +3693,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>S02_1</t>
+          <t>S01_5</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -3707,7 +3703,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>S02_1 Diagnostic des causes — Le conseiller a-t-il cherché à distinguer l'origine du problème (activation du forfait, co</t>
+          <t>S01_5 Pédagogie — Le conseiller a-t-il expliqué les étapes de manière simple et compréhensible, vous permettant de repro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3729,7 +3725,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>S02_1_ALERTE</t>
+          <t>S01_5_ALERTE</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -3757,7 +3753,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>S02_1_COM</t>
+          <t>S01_5_COM</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -3785,7 +3781,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>S02_2</t>
+          <t>S02_1</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -3795,7 +3791,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>S02_2 Vérification de l'activation — Le conseiller a-t-il vérifié que le forfait avait bien été activé sur la ligne ?</t>
+          <t>S02_1 Diagnostic des causes — Le conseiller a-t-il cherché à distinguer l'origine du problème (activation du forfait, co</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3817,7 +3813,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>S02_2_ALERTE</t>
+          <t>S02_1_ALERTE</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -3845,7 +3841,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>S02_2_COM</t>
+          <t>S02_1_COM</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -3873,7 +3869,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>S02_3</t>
+          <t>S02_2</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -3883,7 +3879,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>S02_3 Vérification technique — Le conseiller a-t-il vérifié la configuration (APN, paramètres réseau) et la couverture r</t>
+          <t>S02_2 Vérification de l'activation — Le conseiller a-t-il vérifié que le forfait avait bien été activé sur la ligne ?</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3905,7 +3901,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>S02_3_ALERTE</t>
+          <t>S02_2_ALERTE</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -3933,7 +3929,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>S02_3_COM</t>
+          <t>S02_2_COM</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -3961,7 +3957,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>S02_4</t>
+          <t>S02_3</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -3971,7 +3967,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>S02_4 Solution — Le conseiller a-t-il proposé une solution concrète pour rétablir la navigation ?</t>
+          <t>S02_3 Vérification technique — Le conseiller a-t-il vérifié la configuration (APN, paramètres réseau) et la couverture r</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3993,7 +3989,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>S02_4_ALERTE</t>
+          <t>S02_3_ALERTE</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -4021,7 +4017,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>S02_4_COM</t>
+          <t>S02_3_COM</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -4049,7 +4045,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>S02_5</t>
+          <t>S02_4</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -4059,7 +4055,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>S02_5 Alternative — Le conseiller a-t-il proposé une alternative en cas de non-résolution immédiate (remboursement, gest</t>
+          <t>S02_4 Solution — Le conseiller a-t-il proposé une solution concrète pour rétablir la navigation ?</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4081,7 +4077,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>S02_5_ALERTE</t>
+          <t>S02_4_ALERTE</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -4109,7 +4105,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>S02_5_COM</t>
+          <t>S02_4_COM</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -4137,7 +4133,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>S03_1</t>
+          <t>S02_5</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -4147,7 +4143,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>S03_1 Qualification du problème — Le conseiller a-t-il posé des questions pertinentes pour bien cerner la nature du prob</t>
+          <t>S02_5 Alternative — Le conseiller a-t-il proposé une alternative en cas de non-résolution immédiate (remboursement, gest</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4169,7 +4165,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>S03_1_ALERTE</t>
+          <t>S02_5_ALERTE</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -4197,7 +4193,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>S03_1_COM</t>
+          <t>S02_5_COM</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -4225,7 +4221,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>S03_2</t>
+          <t>S03_1</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -4235,7 +4231,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>S03_2 Localisation — Le conseiller a-t-il vérifié la zone géographique où le problème survient afin d'identifier un éven</t>
+          <t>S03_1 Qualification du problème — Le conseiller a-t-il posé des questions pertinentes pour bien cerner la nature du prob</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4257,7 +4253,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>S03_2_ALERTE</t>
+          <t>S03_1_ALERTE</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -4285,7 +4281,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>S03_2_COM</t>
+          <t>S03_1_COM</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -4313,7 +4309,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>S03_3</t>
+          <t>S03_2</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -4323,7 +4319,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>S03_3 Terminal / SIM — Le conseiller a-t-il demandé des précisions sur le type de téléphone, l'état de la carte SIM ou l</t>
+          <t>S03_2 Localisation — Le conseiller a-t-il vérifié la zone géographique où le problème survient afin d'identifier un éven</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4345,7 +4341,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>S03_3_ALERTE</t>
+          <t>S03_2_ALERTE</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -4373,7 +4369,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>S03_3_COM</t>
+          <t>S03_2_COM</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -4401,7 +4397,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>S03_4</t>
+          <t>S03_3</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -4411,7 +4407,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>S03_4 Incident réseau — Le conseiller a-t-il vérifié s'il existe un incident réseau connu pouvant expliquer les coupures</t>
+          <t>S03_3 Terminal / SIM — Le conseiller a-t-il demandé des précisions sur le type de téléphone, l'état de la carte SIM ou l</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4433,7 +4429,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>S03_4_ALERTE</t>
+          <t>S03_3_ALERTE</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -4461,7 +4457,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>S03_4_COM</t>
+          <t>S03_3_COM</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -4489,7 +4485,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>S03_5</t>
+          <t>S03_4</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -4499,7 +4495,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">S03_5 Solution ou escalade — Le conseiller a-t-il proposé une solution concrète pour résoudre le problème ou, à défaut, </t>
+          <t>S03_4 Incident réseau — Le conseiller a-t-il vérifié s'il existe un incident réseau connu pouvant expliquer les coupures</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4521,7 +4517,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>S03_5_ALERTE</t>
+          <t>S03_4_ALERTE</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -4549,7 +4545,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>S03_5_COM</t>
+          <t>S03_4_COM</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -4577,7 +4573,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>S04_1</t>
+          <t>S03_5</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -4587,7 +4583,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>S04_1 Vérification de la consommation — Le conseiller a-t-il vérifié la consommation réelle du forfait (historique, déta</t>
+          <t xml:space="preserve">S03_5 Solution ou escalade — Le conseiller a-t-il proposé une solution concrète pour résoudre le problème ou, à défaut, </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4609,7 +4605,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>S04_1_ALERTE</t>
+          <t>S03_5_ALERTE</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -4637,7 +4633,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>S04_1_COM</t>
+          <t>S03_5_COM</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -4665,7 +4661,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>S04_2</t>
+          <t>S04_1</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -4675,7 +4671,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>S04_2 Transparence — Le conseiller a-t-il expliqué clairement au client comment son forfait a été consommé aussi rapidem</t>
+          <t>S04_1 Vérification de la consommation — Le conseiller a-t-il vérifié la consommation réelle du forfait (historique, déta</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4697,7 +4693,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>S04_2_ALERTE</t>
+          <t>S04_1_ALERTE</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -4725,7 +4721,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>S04_2_COM</t>
+          <t>S04_1_COM</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -4753,7 +4749,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>S04_3</t>
+          <t>S04_2</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -4763,7 +4759,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>S04_3 Vérification du disponible — Le conseiller a-t-il vérifié s'il existait un reliquat, un bonus ou un forfait complé</t>
+          <t>S04_2 Transparence — Le conseiller a-t-il expliqué clairement au client comment son forfait a été consommé aussi rapidem</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4785,7 +4781,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>S04_3_ALERTE</t>
+          <t>S04_2_ALERTE</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -4813,7 +4809,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>S04_3_COM</t>
+          <t>S04_2_COM</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -4841,7 +4837,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>S04_4</t>
+          <t>S04_3</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -4851,7 +4847,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>S04_4 Conseils de maîtrise — Le conseiller a-t-il donné des conseils pratiques pour mieux maîtriser sa consommation à l'</t>
+          <t>S04_3 Vérification du disponible — Le conseiller a-t-il vérifié s'il existait un reliquat, un bonus ou un forfait complé</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4873,7 +4869,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>S04_4_ALERTE</t>
+          <t>S04_3_ALERTE</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -4901,7 +4897,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>S04_4_COM</t>
+          <t>S04_3_COM</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -4929,7 +4925,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>S05_1</t>
+          <t>S04_4</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -4939,7 +4935,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">S05_1 Investigation — Le conseiller a-t-il mené une investigation rigoureuse pour identifier l'origine du débit (détail </t>
+          <t>S04_4 Conseils de maîtrise — Le conseiller a-t-il donné des conseils pratiques pour mieux maîtriser sa consommation à l'</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4961,7 +4957,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>S05_1_ALERTE</t>
+          <t>S04_4_ALERTE</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -4989,7 +4985,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>S05_1_COM</t>
+          <t>S04_4_COM</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -5017,7 +5013,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>S05_2</t>
+          <t>S05_1</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -5027,7 +5023,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>S05_2 Identification des postes de débit — Le conseiller a-t-il vérifié les différentes sources possibles (data hors for</t>
+          <t xml:space="preserve">S05_1 Investigation — Le conseiller a-t-il mené une investigation rigoureuse pour identifier l'origine du débit (détail </t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5049,7 +5045,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>S05_2_ALERTE</t>
+          <t>S05_1_ALERTE</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -5077,7 +5073,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>S05_2_COM</t>
+          <t>S05_1_COM</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -5105,7 +5101,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>S05_3</t>
+          <t>S05_2</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -5115,7 +5111,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>S05_3 Exactitude — Le conseiller a-t-il fourni des informations exactes et vérifiées sur les montants et la nature des d</t>
+          <t>S05_2 Identification des postes de débit — Le conseiller a-t-il vérifié les différentes sources possibles (data hors for</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5137,7 +5133,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>S05_3_ALERTE</t>
+          <t>S05_2_ALERTE</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -5165,7 +5161,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>S05_3_COM</t>
+          <t>S05_2_COM</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -5193,7 +5189,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>S05_4</t>
+          <t>S05_3</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -5203,7 +5199,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>S05_4 Explication claire — Le conseiller a-t-il expliqué la situation de façon claire et compréhensible pour le client ?</t>
+          <t>S05_3 Exactitude — Le conseiller a-t-il fourni des informations exactes et vérifiées sur les montants et la nature des d</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5225,7 +5221,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>S05_4_ALERTE</t>
+          <t>S05_3_ALERTE</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -5253,7 +5249,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>S05_4_COM</t>
+          <t>S05_3_COM</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -5281,7 +5277,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>S06_1</t>
+          <t>S05_4</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -5291,7 +5287,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>S06_1 Identification du service — Le conseiller a-t-il identifié précisément le service VAS concerné et son mode de sous</t>
+          <t>S05_4 Explication claire — Le conseiller a-t-il expliqué la situation de façon claire et compréhensible pour le client ?</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5313,7 +5309,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>S06_1_ALERTE</t>
+          <t>S05_4_ALERTE</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -5341,7 +5337,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>S06_1_COM</t>
+          <t>S05_4_COM</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -5369,7 +5365,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>S06_2</t>
+          <t>S06_1</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -5379,7 +5375,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>S06_2 Désactivation — Le conseiller a-t-il procédé ou proposé la désactivation immédiate du service ?</t>
+          <t>S06_1 Identification du service — Le conseiller a-t-il identifié précisément le service VAS concerné et son mode de sous</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5401,7 +5397,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>S06_2_ALERTE</t>
+          <t>S06_1_ALERTE</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -5429,7 +5425,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>S06_2_COM</t>
+          <t>S06_1_COM</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -5457,7 +5453,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>S06_3</t>
+          <t>S06_2</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -5467,7 +5463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>S06_3 Procédure de contestation / remboursement — Le conseiller a-t-il expliqué la procédure de contestation et, si appl</t>
+          <t>S06_2 Désactivation — Le conseiller a-t-il procédé ou proposé la désactivation immédiate du service ?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5489,7 +5485,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>S06_3_ALERTE</t>
+          <t>S06_2_ALERTE</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -5517,7 +5513,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>S06_3_COM</t>
+          <t>S06_2_COM</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -5545,7 +5541,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>S06_4</t>
+          <t>S06_3</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -5555,7 +5551,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>S06_4 Rassurance — Le conseiller a-t-il rassuré le client et vérifié qu'aucune autre souscription non désirée n'était ac</t>
+          <t>S06_3 Procédure de contestation / remboursement — Le conseiller a-t-il expliqué la procédure de contestation et, si appl</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5577,7 +5573,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>S06_4_ALERTE</t>
+          <t>S06_3_ALERTE</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -5605,7 +5601,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>S06_4_COM</t>
+          <t>S06_3_COM</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -5633,7 +5629,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>S07_1</t>
+          <t>S06_4</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -5643,7 +5639,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>S07_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause de l'échec de la transaction (solde, canal utilisé</t>
+          <t>S06_4 Rassurance — Le conseiller a-t-il rassuré le client et vérifié qu'aucune autre souscription non désirée n'était ac</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5665,7 +5661,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>S07_1_ALERTE</t>
+          <t>S06_4_ALERTE</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -5693,7 +5689,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>S07_1_COM</t>
+          <t>S06_4_COM</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -5721,7 +5717,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>S07_2</t>
+          <t>S07_1</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -5731,7 +5727,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>S07_2 Connaissance du parcours — Le conseiller a-t-il démontré une bonne connaissance des différents canaux d'achat (USS</t>
+          <t>S07_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause de l'échec de la transaction (solde, canal utilisé</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5753,7 +5749,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>S07_2_ALERTE</t>
+          <t>S07_1_ALERTE</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -5781,7 +5777,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>S07_2_COM</t>
+          <t>S07_1_COM</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -5809,7 +5805,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>S07_3</t>
+          <t>S07_2</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -5819,7 +5815,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>S07_3 Alternatives proposées — Le conseiller a-t-il proposé un canal alternatif pour finaliser l'achat ?</t>
+          <t>S07_2 Connaissance du parcours — Le conseiller a-t-il démontré une bonne connaissance des différents canaux d'achat (USS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5841,7 +5837,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>S07_3_ALERTE</t>
+          <t>S07_2_ALERTE</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -5869,7 +5865,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>S07_3_COM</t>
+          <t>S07_2_COM</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -5897,7 +5893,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>S07_4</t>
+          <t>S07_3</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -5907,7 +5903,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>S07_4 Accompagnement — Le conseiller a-t-il accompagné le client pas à pas jusqu'à la résolution du problème ?</t>
+          <t>S07_3 Alternatives proposées — Le conseiller a-t-il proposé un canal alternatif pour finaliser l'achat ?</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5929,7 +5925,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>S07_4_ALERTE</t>
+          <t>S07_3_ALERTE</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -5957,7 +5953,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>S07_4_COM</t>
+          <t>S07_3_COM</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -5985,7 +5981,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>S08_1</t>
+          <t>S07_4</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -5995,7 +5991,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>S08_1 Assistance digitale — Le conseiller a-t-il apporté une assistance technique adaptée au problème de connexion ?</t>
+          <t>S07_4 Accompagnement — Le conseiller a-t-il accompagné le client pas à pas jusqu'à la résolution du problème ?</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6017,7 +6013,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>S08_1_ALERTE</t>
+          <t>S07_4_ALERTE</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -6045,7 +6041,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>S08_1_COM</t>
+          <t>S07_4_COM</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -6073,7 +6069,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>S08_2</t>
+          <t>S08_1</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -6083,7 +6079,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>S08_2 Étapes simples — Le conseiller a-t-il expliqué les étapes de résolution de manière simple et progressive ?</t>
+          <t>S08_1 Assistance digitale — Le conseiller a-t-il apporté une assistance technique adaptée au problème de connexion ?</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6105,7 +6101,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>S08_2_ALERTE</t>
+          <t>S08_1_ALERTE</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -6133,7 +6129,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>S08_2_COM</t>
+          <t>S08_1_COM</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -6161,7 +6157,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>S08_3</t>
+          <t>S08_2</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -6171,7 +6167,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>S08_3 Récupération d'accès — Le conseiller a-t-il aidé le client à récupérer l'accès à son compte (mot de passe, identif</t>
+          <t>S08_2 Étapes simples — Le conseiller a-t-il expliqué les étapes de résolution de manière simple et progressive ?</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6193,7 +6189,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>S08_3_ALERTE</t>
+          <t>S08_2_ALERTE</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -6221,7 +6217,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>S08_3_COM</t>
+          <t>S08_2_COM</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -6249,7 +6245,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>S08_4</t>
+          <t>S08_3</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -6259,7 +6255,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>S08_4 Alternative — Le conseiller a-t-il proposé une alternative en cas d'indisponibilité prolongée de l'application (US</t>
+          <t>S08_3 Récupération d'accès — Le conseiller a-t-il aidé le client à récupérer l'accès à son compte (mot de passe, identif</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -6281,7 +6277,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>S08_4_ALERTE</t>
+          <t>S08_3_ALERTE</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -6309,7 +6305,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>S08_4_COM</t>
+          <t>S08_3_COM</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -6337,7 +6333,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>S09_1</t>
+          <t>S08_4</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -6347,7 +6343,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>S09_1 Découverte du besoin — Le conseiller a-t-il posé des questions pour bien cerner les besoins et habitudes de consom</t>
+          <t>S08_4 Alternative — Le conseiller a-t-il proposé une alternative en cas d'indisponibilité prolongée de l'application (US</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6369,7 +6365,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>S09_1_ALERTE</t>
+          <t>S08_4_ALERTE</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -6397,7 +6393,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>S09_1_COM</t>
+          <t>S08_4_COM</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -6425,7 +6421,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>S09_2</t>
+          <t>S09_1</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -6435,7 +6431,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>S09_2 Personnalisation — Le conseiller a-t-il adapté sa réponse au profil et au budget exprimés par le client ?</t>
+          <t>S09_1 Découverte du besoin — Le conseiller a-t-il posé des questions pour bien cerner les besoins et habitudes de consom</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -6457,7 +6453,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>S09_2_ALERTE</t>
+          <t>S09_1_ALERTE</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -6485,7 +6481,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>S09_2_COM</t>
+          <t>S09_1_COM</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -6513,7 +6509,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>S09_3</t>
+          <t>S09_2</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -6523,7 +6519,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>S09_3 Connaissance du catalogue — Le conseiller a-t-il démontré une bonne connaissance des offres disponibles ?</t>
+          <t>S09_2 Personnalisation — Le conseiller a-t-il adapté sa réponse au profil et au budget exprimés par le client ?</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6545,7 +6541,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>S09_3_ALERTE</t>
+          <t>S09_2_ALERTE</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -6573,7 +6569,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>S09_3_COM</t>
+          <t>S09_2_COM</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -6601,7 +6597,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>S09_4</t>
+          <t>S09_3</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -6611,7 +6607,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">S09_4 Pertinence de la recommandation — Le conseiller a-t-il proposé un forfait réellement adapté aux besoins exprimés, </t>
+          <t>S09_3 Connaissance du catalogue — Le conseiller a-t-il démontré une bonne connaissance des offres disponibles ?</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6633,7 +6629,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>S09_4_ALERTE</t>
+          <t>S09_3_ALERTE</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -6661,7 +6657,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>S09_4_COM</t>
+          <t>S09_3_COM</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -6689,7 +6685,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>S10_1</t>
+          <t>S09_4</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -6699,7 +6695,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>S10_1 Compréhension de l'usage — Le conseiller a-t-il bien compris les habitudes de consommation actuelles du client ?</t>
+          <t xml:space="preserve">S09_4 Pertinence de la recommandation — Le conseiller a-t-il proposé un forfait réellement adapté aux besoins exprimés, </t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6721,7 +6717,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>S10_1_ALERTE</t>
+          <t>S09_4_ALERTE</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -6749,7 +6745,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>S10_1_COM</t>
+          <t>S09_4_COM</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -6777,7 +6773,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>S10_2</t>
+          <t>S10_1</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -6787,7 +6783,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>S10_2 Présentation des options — Le conseiller a-t-il présenté les différentes options disponibles correspondant à la de</t>
+          <t>S10_1 Compréhension de l'usage — Le conseiller a-t-il bien compris les habitudes de consommation actuelles du client ?</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6809,7 +6805,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>S10_2_ALERTE</t>
+          <t>S10_1_ALERTE</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -6837,7 +6833,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>S10_2_COM</t>
+          <t>S10_1_COM</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -6865,7 +6861,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>S10_3</t>
+          <t>S10_2</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -6875,7 +6871,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>S10_3 Prise en compte des contraintes — Le conseiller a-t-il tenu compte des contraintes du client (engagement, coût, co</t>
+          <t>S10_2 Présentation des options — Le conseiller a-t-il présenté les différentes options disponibles correspondant à la de</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6897,7 +6893,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>S10_3_ALERTE</t>
+          <t>S10_2_ALERTE</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -6925,7 +6921,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>S10_3_COM</t>
+          <t>S10_2_COM</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -6953,7 +6949,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>S10_4</t>
+          <t>S10_3</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -6963,7 +6959,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>S10_4 Conseil adapté — Le conseiller a-t-il proposé une offre réellement adaptée à la demande du client ?</t>
+          <t>S10_3 Prise en compte des contraintes — Le conseiller a-t-il tenu compte des contraintes du client (engagement, coût, co</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6985,7 +6981,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>S10_4_ALERTE</t>
+          <t>S10_3_ALERTE</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -7013,7 +7009,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>S10_4_COM</t>
+          <t>S10_3_COM</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -7041,7 +7037,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>S10_5</t>
+          <t>S10_4</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -7051,7 +7047,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>S10_5 Absence de vente forcée — Le conseiller a-t-il respecté le choix du client sans forcer une offre plus chère ou non</t>
+          <t>S10_4 Conseil adapté — Le conseiller a-t-il proposé une offre réellement adaptée à la demande du client ?</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -7073,7 +7069,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>S10_5_ALERTE</t>
+          <t>S10_4_ALERTE</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -7101,7 +7097,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>S10_5_COM</t>
+          <t>S10_4_COM</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -7129,7 +7125,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>S11_1</t>
+          <t>S10_5</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -7139,7 +7135,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>S11_1 Authentification — Le conseiller a-t-il procédé à une vérification d'identité conforme avant de communiquer le cod</t>
+          <t>S10_5 Absence de vente forcée — Le conseiller a-t-il respecté le choix du client sans forcer une offre plus chère ou non</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -7161,7 +7157,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>S11_1_ALERTE</t>
+          <t>S10_5_ALERTE</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -7189,7 +7185,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>S11_1_COM</t>
+          <t>S10_5_COM</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -7217,7 +7213,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>S11_2</t>
+          <t>S11_1</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -7227,7 +7223,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>S11_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité tout au long de l'échange ?</t>
+          <t>S11_1 Authentification — Le conseiller a-t-il procédé à une vérification d'identité conforme avant de communiquer le cod</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7249,7 +7245,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>S11_2_ALERTE</t>
+          <t>S11_1_ALERTE</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -7277,7 +7273,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>S11_2_COM</t>
+          <t>S11_1_COM</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -7305,7 +7301,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>S11_3</t>
+          <t>S11_2</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -7315,7 +7311,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>S11_3 Rapidité de résolution — Le conseiller a-t-il résolu la situation rapidement et efficacement ?</t>
+          <t>S11_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité tout au long de l'échange ?</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -7337,7 +7333,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>S11_3_ALERTE</t>
+          <t>S11_2_ALERTE</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -7365,7 +7361,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>S11_3_COM</t>
+          <t>S11_2_COM</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -7393,7 +7389,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>S11_4</t>
+          <t>S11_3</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -7403,7 +7399,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>S11_4 Pédagogie — Le conseiller a-t-il expliqué au client comment éviter ce type de blocage à l'avenir ?</t>
+          <t>S11_3 Rapidité de résolution — Le conseiller a-t-il résolu la situation rapidement et efficacement ?</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -7425,7 +7421,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>S11_4_ALERTE</t>
+          <t>S11_3_ALERTE</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -7453,7 +7449,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>S11_4_COM</t>
+          <t>S11_3_COM</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -7481,7 +7477,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>S12_1</t>
+          <t>S11_4</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -7491,7 +7487,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>S12_1 Priorisation de la sécurité — Le conseiller a-t-il traité la demande en priorité, avec le sérieux requis par la si</t>
+          <t>S11_4 Pédagogie — Le conseiller a-t-il expliqué au client comment éviter ce type de blocage à l'avenir ?</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -7513,7 +7509,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>S12_1_ALERTE</t>
+          <t>S11_4_ALERTE</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -7541,7 +7537,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>S12_1_COM</t>
+          <t>S11_4_COM</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -7569,7 +7565,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>S12_2</t>
+          <t>S12_1</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -7579,7 +7575,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>S12_2 Blocage / protection — Le conseiller a-t-il procédé ou guidé le client vers le blocage immédiat de la ligne ?</t>
+          <t>S12_1 Priorisation de la sécurité — Le conseiller a-t-il traité la demande en priorité, avec le sérieux requis par la si</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7601,7 +7597,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>S12_2_ALERTE</t>
+          <t>S12_1_ALERTE</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -7629,7 +7625,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>S12_2_COM</t>
+          <t>S12_1_COM</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -7657,7 +7653,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>S12_3</t>
+          <t>S12_2</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -7667,7 +7663,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>S12_3 Authentification — Le conseiller a-t-il vérifié l'identité du client selon la procédure requise avant toute action</t>
+          <t>S12_2 Blocage / protection — Le conseiller a-t-il procédé ou guidé le client vers le blocage immédiat de la ligne ?</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7689,7 +7685,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>S12_3_ALERTE</t>
+          <t>S12_2_ALERTE</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -7717,7 +7713,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>S12_3_COM</t>
+          <t>S12_2_COM</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -7745,7 +7741,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>S12_4</t>
+          <t>S12_3</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -7755,7 +7751,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>S12_4 Procédure de remplacement — Le conseiller a-t-il expliqué clairement la procédure pour obtenir une nouvelle SIM ?</t>
+          <t>S12_3 Authentification — Le conseiller a-t-il vérifié l'identité du client selon la procédure requise avant toute action</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7777,7 +7773,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>S12_4_ALERTE</t>
+          <t>S12_3_ALERTE</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -7805,7 +7801,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>S12_4_COM</t>
+          <t>S12_3_COM</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -7833,7 +7829,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>S13_1</t>
+          <t>S12_4</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -7843,7 +7839,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>S13_1 Maîtrise KYC — Le conseiller a-t-il fait preuve d'une bonne maîtrise des règles d'identification (KYC) applicables</t>
+          <t>S12_4 Procédure de remplacement — Le conseiller a-t-il expliqué clairement la procédure pour obtenir une nouvelle SIM ?</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7865,7 +7861,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>S13_1_ALERTE</t>
+          <t>S12_4_ALERTE</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -7893,7 +7889,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>S13_1_COM</t>
+          <t>S12_4_COM</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -7921,7 +7917,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>S13_2</t>
+          <t>S13_1</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -7931,7 +7927,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>S13_2 Clarté de la procédure — Le conseiller a-t-il expliqué clairement la procédure à suivre pour régulariser la situat</t>
+          <t>S13_1 Maîtrise KYC — Le conseiller a-t-il fait preuve d'une bonne maîtrise des règles d'identification (KYC) applicables</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7953,7 +7949,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>S13_2_ALERTE</t>
+          <t>S13_1_ALERTE</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -7981,7 +7977,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>S13_2_COM</t>
+          <t>S13_1_COM</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -8009,7 +8005,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>S13_3</t>
+          <t>S13_2</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -8019,7 +8015,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>S13_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives nécessaires et le canal à utiliser ?</t>
+          <t>S13_2 Clarté de la procédure — Le conseiller a-t-il expliqué clairement la procédure à suivre pour régulariser la situat</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8041,7 +8037,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>S13_3_ALERTE</t>
+          <t>S13_2_ALERTE</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -8069,7 +8065,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>S13_3_COM</t>
+          <t>S13_2_COM</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -8097,7 +8093,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>S13_4</t>
+          <t>S13_3</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -8107,7 +8103,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">S13_4 Minimisation de l'effort — Le conseiller a-t-il proposé la solution la plus simple et la moins contraignante pour </t>
+          <t>S13_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives nécessaires et le canal à utiliser ?</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -8129,7 +8125,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>S13_4_ALERTE</t>
+          <t>S13_3_ALERTE</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -8157,7 +8153,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>S13_4_COM</t>
+          <t>S13_3_COM</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -8185,7 +8181,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>S14_1</t>
+          <t>S13_4</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -8195,7 +8191,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>S14_1 Consultation de l'historique — Le conseiller a-t-il consulté l'historique des échanges précédents avant de répondr</t>
+          <t xml:space="preserve">S13_4 Minimisation de l'effort — Le conseiller a-t-il proposé la solution la plus simple et la moins contraignante pour </t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -8217,7 +8213,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>S14_1_ALERTE</t>
+          <t>S13_4_ALERTE</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -8245,7 +8241,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>S14_1_COM</t>
+          <t>S13_4_COM</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -8273,7 +8269,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>S14_2</t>
+          <t>S14_1</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -8283,7 +8279,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>S14_2 Reconnaissance de la récurrence — Le conseiller a-t-il reconnu explicitement le caractère récurrent du problème ?</t>
+          <t>S14_1 Consultation de l'historique — Le conseiller a-t-il consulté l'historique des échanges précédents avant de répondr</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -8305,7 +8301,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>S14_2_ALERTE</t>
+          <t>S14_1_ALERTE</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -8333,7 +8329,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>S14_2_COM</t>
+          <t>S14_1_COM</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -8361,7 +8357,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>S14_3</t>
+          <t>S14_2</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -8371,7 +8367,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>S14_3 Ownership — Le conseiller a-t-il pris en charge la demande sans renvoyer la responsabilité au client ?</t>
+          <t>S14_2 Reconnaissance de la récurrence — Le conseiller a-t-il reconnu explicitement le caractère récurrent du problème ?</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -8393,7 +8389,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>S14_3_ALERTE</t>
+          <t>S14_2_ALERTE</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -8421,7 +8417,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>S14_3_COM</t>
+          <t>S14_2_COM</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -8449,7 +8445,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>S14_4</t>
+          <t>S14_3</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -8459,7 +8455,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>S14_4 Escalade appropriée — Le conseiller a-t-il procédé à une escalade adaptée si nécessaire ?</t>
+          <t>S14_3 Ownership — Le conseiller a-t-il pris en charge la demande sans renvoyer la responsabilité au client ?</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -8481,7 +8477,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>S14_4_ALERTE</t>
+          <t>S14_3_ALERTE</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -8509,7 +8505,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>S14_4_COM</t>
+          <t>S14_3_COM</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -8537,7 +8533,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>S14_5</t>
+          <t>S14_4</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -8547,7 +8543,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>S14_5 Délai / next step — Le conseiller a-t-il communiqué un délai clair et une prochaine étape précise ?</t>
+          <t>S14_4 Escalade appropriée — Le conseiller a-t-il procédé à une escalade adaptée si nécessaire ?</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -8569,7 +8565,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>S14_5_ALERTE</t>
+          <t>S14_4_ALERTE</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -8597,7 +8593,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>S14_5_COM</t>
+          <t>S14_4_COM</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -8625,7 +8621,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>S15_1</t>
+          <t>S14_5</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -8635,7 +8631,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>S15_1 Écoute émotionnelle — Le conseiller a-t-il su écouter le mécontentement du client sans l'interrompre ni se justifi</t>
+          <t>S14_5 Délai / next step — Le conseiller a-t-il communiqué un délai clair et une prochaine étape précise ?</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8657,7 +8653,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>S15_1_ALERTE</t>
+          <t>S14_5_ALERTE</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -8685,7 +8681,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>S15_1_COM</t>
+          <t>S14_5_COM</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -8713,7 +8709,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>S15_2</t>
+          <t>S15_1</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -8723,7 +8719,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>S15_2 Désescalade — Le conseiller a-t-il su désamorcer la tension par son attitude et son discours ?</t>
+          <t>S15_1 Écoute émotionnelle — Le conseiller a-t-il su écouter le mécontentement du client sans l'interrompre ni se justifi</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8745,7 +8741,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>S15_2_ALERTE</t>
+          <t>S15_1_ALERTE</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -8773,7 +8769,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>S15_2_COM</t>
+          <t>S15_1_COM</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -8801,7 +8797,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>S15_3</t>
+          <t>S15_2</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -8811,7 +8807,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S15_3 Empathie — Le conseiller a-t-il exprimé de l'empathie envers la situation vécue par le client ?</t>
+          <t>S15_2 Désescalade — Le conseiller a-t-il su désamorcer la tension par son attitude et son discours ?</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8833,7 +8829,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>S15_3_ALERTE</t>
+          <t>S15_2_ALERTE</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -8861,7 +8857,7 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>S15_3_COM</t>
+          <t>S15_2_COM</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -8889,7 +8885,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>S15_4</t>
+          <t>S15_3</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -8899,7 +8895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>S15_4 Reprise en main — Le conseiller a-t-il repris le contrôle de l'échange de façon professionnelle et rassurante ?</t>
+          <t>S15_3 Empathie — Le conseiller a-t-il exprimé de l'empathie envers la situation vécue par le client ?</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8921,7 +8917,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>S15_4_ALERTE</t>
+          <t>S15_3_ALERTE</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -8949,7 +8945,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>S15_4_COM</t>
+          <t>S15_3_COM</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -8977,7 +8973,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>S15_5</t>
+          <t>S15_4</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -8987,7 +8983,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>S15_5 Recherche de solution — Le conseiller a-t-il orienté l'échange vers une recherche concrète de solution ?</t>
+          <t>S15_4 Reprise en main — Le conseiller a-t-il repris le contrôle de l'échange de façon professionnelle et rassurante ?</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9009,7 +9005,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>S15_5_ALERTE</t>
+          <t>S15_4_ALERTE</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -9037,7 +9033,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>S15_5_COM</t>
+          <t>S15_4_COM</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -9065,7 +9061,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>S16_1</t>
+          <t>S15_5</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -9075,7 +9071,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>S16_1 Rapidité — Le conseiller a-t-il répondu rapidement à la demande ?</t>
+          <t>S15_5 Recherche de solution — Le conseiller a-t-il orienté l'échange vers une recherche concrète de solution ?</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9097,7 +9093,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>S16_1_ALERTE</t>
+          <t>S15_5_ALERTE</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -9125,7 +9121,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>S16_1_COM</t>
+          <t>S15_5_COM</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -9153,7 +9149,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>S16_2</t>
+          <t>S16_1</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -9163,7 +9159,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>S16_2 Exactitude — L'information tarifaire communiquée était-elle exacte ?</t>
+          <t>S16_1 Rapidité — Le conseiller a-t-il répondu rapidement à la demande ?</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -9185,7 +9181,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>S16_2_ALERTE</t>
+          <t>S16_1_ALERTE</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -9213,7 +9209,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>S16_2_COM</t>
+          <t>S16_1_COM</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -9241,7 +9237,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>S16_3</t>
+          <t>S16_2</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -9251,7 +9247,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>S16_3 Simplicité — La réponse a-t-elle été formulée de façon simple et directement compréhensible ?</t>
+          <t>S16_2 Exactitude — L'information tarifaire communiquée était-elle exacte ?</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -9273,7 +9269,7 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>S16_3_ALERTE</t>
+          <t>S16_2_ALERTE</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -9301,7 +9297,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>S16_3_COM</t>
+          <t>S16_2_COM</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -9329,7 +9325,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>S16_4</t>
+          <t>S16_3</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -9339,7 +9335,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S16_4 Absence d'informations inutiles — Le conseiller a-t-il évité de noyer la réponse dans des informations non demandé</t>
+          <t>S16_3 Simplicité — La réponse a-t-elle été formulée de façon simple et directement compréhensible ?</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -9361,7 +9357,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>S16_4_ALERTE</t>
+          <t>S16_3_ALERTE</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -9389,7 +9385,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>S16_4_COM</t>
+          <t>S16_3_COM</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -9417,7 +9413,7 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>S17_1</t>
+          <t>S16_4</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -9427,7 +9423,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>S17_1 Maîtrise du roaming — Le conseiller a-t-il démontré une bonne connaissance des conditions d'utilisation à l'étrang</t>
+          <t>S16_4 Absence d'informations inutiles — Le conseiller a-t-il évité de noyer la réponse dans des informations non demandé</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -9449,7 +9445,7 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>S17_1_ALERTE</t>
+          <t>S16_4_ALERTE</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -9477,7 +9473,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>S17_1_COM</t>
+          <t>S16_4_COM</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -9505,7 +9501,7 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>S17_2</t>
+          <t>S17_1</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -9515,7 +9511,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>S17_2 Conditions d'activation — Le conseiller a-t-il expliqué les éventuelles conditions d'activation du roaming ?</t>
+          <t>S17_1 Maîtrise du roaming — Le conseiller a-t-il démontré une bonne connaissance des conditions d'utilisation à l'étrang</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -9537,7 +9533,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>S17_2_ALERTE</t>
+          <t>S17_1_ALERTE</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -9565,7 +9561,7 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>S17_2_COM</t>
+          <t>S17_1_COM</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -9593,7 +9589,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>S17_3</t>
+          <t>S17_2</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -9603,7 +9599,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>S17_3 Tarification — Le conseiller a-t-il communiqué une information tarifaire claire et exacte pour la destination conc</t>
+          <t>S17_2 Conditions d'activation — Le conseiller a-t-il expliqué les éventuelles conditions d'activation du roaming ?</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -9625,7 +9621,7 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>S17_3_ALERTE</t>
+          <t>S17_2_ALERTE</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -9653,7 +9649,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>S17_3_COM</t>
+          <t>S17_2_COM</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -9681,7 +9677,7 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>S17_4</t>
+          <t>S17_3</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -9691,7 +9687,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>S17_4 Prévention du hors-forfait — Le conseiller a-t-il alerté le client sur les risques de hors-forfait et les moyens d</t>
+          <t>S17_3 Tarification — Le conseiller a-t-il communiqué une information tarifaire claire et exacte pour la destination conc</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -9713,7 +9709,7 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>S17_4_ALERTE</t>
+          <t>S17_3_ALERTE</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -9741,7 +9737,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>S17_4_COM</t>
+          <t>S17_3_COM</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -9769,7 +9765,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>S17_5</t>
+          <t>S17_4</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -9779,7 +9775,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>S17_5 Conseil — Le conseiller a-t-il proposé une offre ou un conseil adapté au voyage du client ?</t>
+          <t>S17_4 Prévention du hors-forfait — Le conseiller a-t-il alerté le client sur les risques de hors-forfait et les moyens d</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9801,7 +9797,7 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>S17_5_ALERTE</t>
+          <t>S17_4_ALERTE</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -9829,7 +9825,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>S17_5_COM</t>
+          <t>S17_4_COM</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -9857,7 +9853,7 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>S18_1</t>
+          <t>S17_5</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -9867,7 +9863,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>S18_1 Connaissance des canaux — Le conseiller a-t-il démontré une bonne connaissance des procédures via USSD et/ou appli</t>
+          <t>S17_5 Conseil — Le conseiller a-t-il proposé une offre ou un conseil adapté au voyage du client ?</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9889,7 +9885,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>S18_1_ALERTE</t>
+          <t>S17_5_ALERTE</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -9917,7 +9913,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>S18_1_COM</t>
+          <t>S17_5_COM</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -9945,7 +9941,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>S18_2</t>
+          <t>S18_1</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -9955,7 +9951,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S18_2 Explication pas-à-pas — Le conseiller a-t-il expliqué la procédure de manière claire et détaillée, étape par étape</t>
+          <t>S18_1 Connaissance des canaux — Le conseiller a-t-il démontré une bonne connaissance des procédures via USSD et/ou appli</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9977,7 +9973,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>S18_2_ALERTE</t>
+          <t>S18_1_ALERTE</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -10005,7 +10001,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>S18_2_COM</t>
+          <t>S18_1_COM</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -10033,7 +10029,7 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>S18_3</t>
+          <t>S18_2</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -10043,7 +10039,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>S18_3 Frais et conditions — Le conseiller a-t-il informé le client des éventuels frais ou conditions applicables au tran</t>
+          <t>S18_2 Explication pas-à-pas — Le conseiller a-t-il expliqué la procédure de manière claire et détaillée, étape par étape</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10065,7 +10061,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>S18_3_ALERTE</t>
+          <t>S18_2_ALERTE</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -10093,7 +10089,7 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>S18_3_COM</t>
+          <t>S18_2_COM</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -10121,7 +10117,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>S19_1</t>
+          <t>S18_3</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -10131,7 +10127,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>S19_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause probable du problème (délai technique, erreur de n</t>
+          <t>S18_3 Frais et conditions — Le conseiller a-t-il informé le client des éventuels frais ou conditions applicables au tran</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10153,7 +10149,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>S19_1_ALERTE</t>
+          <t>S18_3_ALERTE</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -10181,7 +10177,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>S19_1_COM</t>
+          <t>S18_3_COM</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -10209,7 +10205,7 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>S19_2</t>
+          <t>S19_1</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -10219,7 +10215,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>S19_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité et de vérification d'identité propres au Mobil</t>
+          <t>S19_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause probable du problème (délai technique, erreur de n</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10241,7 +10237,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>S19_2_ALERTE</t>
+          <t>S19_1_ALERTE</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -10269,7 +10265,7 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>S19_2_COM</t>
+          <t>S19_1_COM</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -10297,7 +10293,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>S19_3</t>
+          <t>S19_2</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -10307,7 +10303,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>S19_3 Traçabilité — Le conseiller a-t-il vérifié la transaction à l'aide des références fournies par le client ?</t>
+          <t>S19_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité et de vérification d'identité propres au Mobil</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -10329,7 +10325,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>S19_3_ALERTE</t>
+          <t>S19_2_ALERTE</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -10357,7 +10353,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>S19_3_COM</t>
+          <t>S19_2_COM</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -10385,7 +10381,7 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>S19_4</t>
+          <t>S19_3</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -10395,7 +10391,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S19_4 Procédure de réclamation et délai — Le conseiller a-t-il expliqué la procédure de réclamation et communiqué un dél</t>
+          <t>S19_3 Traçabilité — Le conseiller a-t-il vérifié la transaction à l'aide des références fournies par le client ?</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10417,7 +10413,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>S19_4_ALERTE</t>
+          <t>S19_3_ALERTE</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -10445,7 +10441,7 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>S19_4_COM</t>
+          <t>S19_3_COM</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -10473,7 +10469,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>S20_1</t>
+          <t>S19_4</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -10483,7 +10479,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>S20_1 Maîtrise de la procédure — Le conseiller a-t-il connu et expliqué correctement la procédure applicable à ce type d</t>
+          <t>S19_4 Procédure de réclamation et délai — Le conseiller a-t-il expliqué la procédure de réclamation et communiqué un dél</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -10505,7 +10501,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>S20_1_ALERTE</t>
+          <t>S19_4_ALERTE</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -10533,7 +10529,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>S20_1_COM</t>
+          <t>S19_4_COM</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -10561,7 +10557,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>S20_2</t>
+          <t>S20_1</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -10571,7 +10567,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>S20_2 Gestion du risque — Le conseiller a-t-il agi avec la prudence nécessaire compte tenu de la sensibilité de l'opérat</t>
+          <t>S20_1 Maîtrise de la procédure — Le conseiller a-t-il connu et expliqué correctement la procédure applicable à ce type d</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -10593,7 +10589,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>S20_2_ALERTE</t>
+          <t>S20_1_ALERTE</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -10621,7 +10617,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>S20_2_COM</t>
+          <t>S20_1_COM</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -10649,7 +10645,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>S20_3</t>
+          <t>S20_2</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -10659,7 +10655,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>S20_3 Transparence — Le conseiller a-t-il été transparent sur les possibilités réelles d'annulation ou de récupération d</t>
+          <t>S20_2 Gestion du risque — Le conseiller a-t-il agi avec la prudence nécessaire compte tenu de la sensibilité de l'opérat</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -10681,7 +10677,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>S20_3_ALERTE</t>
+          <t>S20_2_ALERTE</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -10709,7 +10705,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>S20_3_COM</t>
+          <t>S20_2_COM</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -10737,7 +10733,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>S20_4</t>
+          <t>S20_3</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -10747,7 +10743,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>S20_4 Accompagnement — Le conseiller a-t-il guidé le client sur les démarches à suivre (délai, pièces, contact du bénéfi</t>
+          <t>S20_3 Transparence — Le conseiller a-t-il été transparent sur les possibilités réelles d'annulation ou de récupération d</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -10769,7 +10765,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>S20_4_ALERTE</t>
+          <t>S20_3_ALERTE</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -10797,7 +10793,7 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>S20_4_COM</t>
+          <t>S20_3_COM</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -10825,7 +10821,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>S21_1</t>
+          <t>S20_4</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -10835,7 +10831,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>S21_1 Maîtrise des règles de cycle de vie — Le conseiller a-t-il expliqué correctement les règles de désactivation et de</t>
+          <t>S20_4 Accompagnement — Le conseiller a-t-il guidé le client sur les démarches à suivre (délai, pièces, contact du bénéfi</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10857,7 +10853,7 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>S21_1_ALERTE</t>
+          <t>S20_4_ALERTE</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -10885,7 +10881,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>S21_1_COM</t>
+          <t>S20_4_COM</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -10913,7 +10909,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>S21_2</t>
+          <t>S21_1</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -10923,7 +10919,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>S21_2 Vérification de la disponibilité — Le conseiller a-t-il vérifié si le numéro était encore disponible pour une réac</t>
+          <t>S21_1 Maîtrise des règles de cycle de vie — Le conseiller a-t-il expliqué correctement les règles de désactivation et de</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10945,7 +10941,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>S21_2_ALERTE</t>
+          <t>S21_1_ALERTE</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -10973,7 +10969,7 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>S21_2_COM</t>
+          <t>S21_1_COM</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -11001,7 +10997,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>S21_3</t>
+          <t>S21_2</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -11011,7 +11007,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>S21_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives et le canal à utiliser pour la démarche ?</t>
+          <t>S21_2 Vérification de la disponibilité — Le conseiller a-t-il vérifié si le numéro était encore disponible pour une réac</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -11033,7 +11029,7 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>S21_3_ALERTE</t>
+          <t>S21_2_ALERTE</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -11061,7 +11057,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>S21_3_COM</t>
+          <t>S21_2_COM</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -11089,7 +11085,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>S21_4</t>
+          <t>S21_3</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -11099,7 +11095,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>S21_4 Alternatives — Le conseiller a-t-il proposé une alternative si le numéro n'était plus récupérable ?</t>
+          <t>S21_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives et le canal à utiliser pour la démarche ?</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -11121,7 +11117,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>S21_4_ALERTE</t>
+          <t>S21_3_ALERTE</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -11149,7 +11145,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>S21_4_COM</t>
+          <t>S21_3_COM</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -11177,7 +11173,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>S22_1</t>
+          <t>S21_4</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -11187,7 +11183,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>S22_1 Vérification d'incident — Le conseiller a-t-il vérifié l'existence d'un incident réseau connu dans la zone concern</t>
+          <t>S21_4 Alternatives — Le conseiller a-t-il proposé une alternative si le numéro n'était plus récupérable ?</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -11209,7 +11205,7 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>S22_1_ALERTE</t>
+          <t>S21_4_ALERTE</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -11237,7 +11233,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>S22_1_COM</t>
+          <t>S21_4_COM</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -11265,7 +11261,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>S22_2</t>
+          <t>S22_1</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -11275,7 +11271,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>S22_2 Collecte de la localisation — Le conseiller a-t-il précisément recueilli la localisation du client (quartier, vill</t>
+          <t>S22_1 Vérification d'incident — Le conseiller a-t-il vérifié l'existence d'un incident réseau connu dans la zone concern</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -11297,7 +11293,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>S22_2_ALERTE</t>
+          <t>S22_1_ALERTE</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -11325,7 +11321,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>S22_2_COM</t>
+          <t>S22_1_COM</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -11353,7 +11349,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>S22_3</t>
+          <t>S22_2</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -11363,7 +11359,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>S22_3 Communication proactive — Le conseiller a-t-il communiqué de façon proactive sur l'état de la situation ?</t>
+          <t>S22_2 Collecte de la localisation — Le conseiller a-t-il précisément recueilli la localisation du client (quartier, vill</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -11385,7 +11381,7 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>S22_3_ALERTE</t>
+          <t>S22_2_ALERTE</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -11413,7 +11409,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>S22_3_COM</t>
+          <t>S22_2_COM</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -11441,7 +11437,7 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>S22_4</t>
+          <t>S22_3</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -11451,7 +11447,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>S22_4 Délai / next step — Le conseiller a-t-il donné un délai ou une prochaine étape claire au client ?</t>
+          <t>S22_3 Communication proactive — Le conseiller a-t-il communiqué de façon proactive sur l'état de la situation ?</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -11473,7 +11469,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>S22_4_ALERTE</t>
+          <t>S22_3_ALERTE</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -11501,7 +11497,7 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>S22_4_COM</t>
+          <t>S22_3_COM</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -11529,7 +11525,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>S23_1</t>
+          <t>S22_4</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -11539,7 +11535,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>S23_1 Capacité d'adaptation — Le conseiller a-t-il su adapter sa reformulation à la demande du client ?</t>
+          <t>S22_4 Délai / next step — Le conseiller a-t-il donné un délai ou une prochaine étape claire au client ?</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -11561,7 +11557,7 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>S23_1_ALERTE</t>
+          <t>S22_4_ALERTE</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -11589,7 +11585,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>S23_1_COM</t>
+          <t>S22_4_COM</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -11617,7 +11613,7 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>S23_2</t>
+          <t>S23_1</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -11627,7 +11623,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>S23_2 Patience — Le conseiller a-t-il fait preuve de patience face à la demande de réexplication ?</t>
+          <t>S23_1 Capacité d'adaptation — Le conseiller a-t-il su adapter sa reformulation à la demande du client ?</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -11649,7 +11645,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>S23_2_ALERTE</t>
+          <t>S23_1_ALERTE</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -11677,7 +11673,7 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>S23_2_COM</t>
+          <t>S23_1_COM</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -11705,7 +11701,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>S23_3</t>
+          <t>S23_2</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -11715,7 +11711,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>S23_3 Langage simple — Le conseiller a-t-il reformulé son explication avec des mots simples, sans jargon technique ?</t>
+          <t>S23_2 Patience — Le conseiller a-t-il fait preuve de patience face à la demande de réexplication ?</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -11737,7 +11733,7 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>S23_3_ALERTE</t>
+          <t>S23_2_ALERTE</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -11765,7 +11761,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>S23_3_COM</t>
+          <t>S23_2_COM</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -11793,7 +11789,7 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>S23_4</t>
+          <t>S23_3</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -11803,7 +11799,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>S23_4 Vérification de compréhension — Le conseiller a-t-il vérifié, à la fin de son explication, que le client avait bie</t>
+          <t>S23_3 Langage simple — Le conseiller a-t-il reformulé son explication avec des mots simples, sans jargon technique ?</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -11825,7 +11821,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>S23_4_ALERTE</t>
+          <t>S23_3_ALERTE</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -11853,7 +11849,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>S23_4_COM</t>
+          <t>S23_3_COM</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -11881,7 +11877,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>S24_1</t>
+          <t>S23_4</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -11891,7 +11887,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>S24_1 Inclusion — Le conseiller a-t-il adapté son discours et son rythme au niveau d'aisance digitale du client ?</t>
+          <t>S23_4 Vérification de compréhension — Le conseiller a-t-il vérifié, à la fin de son explication, que le client avait bie</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11913,7 +11909,7 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>S24_1_ALERTE</t>
+          <t>S23_4_ALERTE</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -11941,7 +11937,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>S24_1_COM</t>
+          <t>S23_4_COM</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -11969,7 +11965,7 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>S24_2</t>
+          <t>S24_1</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -11979,7 +11975,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>S24_2 Patience — Le conseiller a-t-il fait preuve de patience tout au long de l'accompagnement ?</t>
+          <t>S24_1 Inclusion — Le conseiller a-t-il adapté son discours et son rythme au niveau d'aisance digitale du client ?</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -12001,7 +11997,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>S24_2_ALERTE</t>
+          <t>S24_1_ALERTE</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -12029,7 +12025,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>S24_2_COM</t>
+          <t>S24_1_COM</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -12057,7 +12053,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>S24_3</t>
+          <t>S24_2</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -12067,7 +12063,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>S24_3 Guidage étape par étape — Le conseiller a-t-il guidé le client pas à pas dans la réalisation de l'opération ?</t>
+          <t>S24_2 Patience — Le conseiller a-t-il fait preuve de patience tout au long de l'accompagnement ?</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -12089,7 +12085,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>S24_3_ALERTE</t>
+          <t>S24_2_ALERTE</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -12117,7 +12113,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>S24_3_COM</t>
+          <t>S24_2_COM</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -12145,7 +12141,7 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>S24_4</t>
+          <t>S24_3</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -12155,7 +12151,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>S24_4 Alternative non digitale — Le conseiller a-t-il proposé, si utile, une alternative non digitale (USSD, agence) ?</t>
+          <t>S24_3 Guidage étape par étape — Le conseiller a-t-il guidé le client pas à pas dans la réalisation de l'opération ?</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -12177,7 +12173,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>S24_4_ALERTE</t>
+          <t>S24_3_ALERTE</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -12205,7 +12201,7 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>S24_4_COM</t>
+          <t>S24_3_COM</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -12233,7 +12229,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>S25_1</t>
+          <t>S24_4</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -12243,7 +12239,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>S25_1 Ownership — Le conseiller a-t-il pris la demande en charge sans se défausser immédiatement ?</t>
+          <t>S24_4 Alternative non digitale — Le conseiller a-t-il proposé, si utile, une alternative non digitale (USSD, agence) ?</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -12265,7 +12261,7 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>S25_1_ALERTE</t>
+          <t>S24_4_ALERTE</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -12293,7 +12289,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>S25_1_COM</t>
+          <t>S24_4_COM</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -12321,7 +12317,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>S25_2</t>
+          <t>S25_1</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -12331,7 +12327,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>S25_2 Capacité d'orientation — Le conseiller a-t-il su orienter le client vers le bon service ou canal de traitement ?</t>
+          <t>S25_1 Ownership — Le conseiller a-t-il pris la demande en charge sans se défausser immédiatement ?</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -12353,7 +12349,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>S25_2_ALERTE</t>
+          <t>S25_1_ALERTE</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -12381,7 +12377,7 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>S25_2_COM</t>
+          <t>S25_1_COM</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -12409,7 +12405,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>S25_3</t>
+          <t>S25_2</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -12419,7 +12415,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>S25_3 Enregistrement de la plainte — Le conseiller a-t-il procédé ou proposé l'enregistrement formel de la réclamation ?</t>
+          <t>S25_2 Capacité d'orientation — Le conseiller a-t-il su orienter le client vers le bon service ou canal de traitement ?</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -12441,7 +12437,7 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>S25_3_ALERTE</t>
+          <t>S25_2_ALERTE</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -12469,7 +12465,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>S25_3_COM</t>
+          <t>S25_2_COM</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -12497,7 +12493,7 @@
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>S25_4</t>
+          <t>S25_3</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -12507,7 +12503,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>S25_4 Absence de renvoi abusif — Le conseiller a-t-il évité tout renvoi injustifié ou toute fin de non-recevoir ?</t>
+          <t>S25_3 Enregistrement de la plainte — Le conseiller a-t-il procédé ou proposé l'enregistrement formel de la réclamation ?</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -12529,7 +12525,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>S25_4_ALERTE</t>
+          <t>S25_3_ALERTE</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -12557,7 +12553,7 @@
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>S25_4_COM</t>
+          <t>S25_3_COM</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -12585,7 +12581,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>SCORE_I</t>
+          <t>S25_4</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -12595,15 +12591,19 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Score — Maîtrise du scénario</t>
+          <t>S25_4 Absence de renvoi abusif — Le conseiller a-t-il évité tout renvoi injustifié ou toute fin de non-recevoir ?</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>section I</t>
+        </is>
+      </c>
       <c r="F416" t="inlineStr">
         <is>
           <t>I. MAÎTRISE DU SCÉNARIO</t>
@@ -12613,7 +12613,7 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>S25_4_ALERTE</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -12623,25 +12623,25 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Q24 Quel est le principal point fort de cet appel ?</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_nc</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Synthèse qualitative</t>
+          <t>I. MAÎTRISE DU SCÉNARIO</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>S25_4_COM</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Q25 Quel est le principal irritant ou effort subi par le client ?</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -12662,14 +12662,14 @@
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Synthèse qualitative</t>
+          <t>I. MAÎTRISE DU SCÉNARIO</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>SCORE_I</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -12679,25 +12679,25 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Q26 Le client devrait-il rappeler ou contacter un autre canal pour le même motif ?</t>
+          <t>Score — Maîtrise du scénario</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>select_one oui_non</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Synthèse qualitative</t>
+          <t>I. MAÎTRISE DU SCÉNARIO</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>Q26_TXT</t>
+          <t>Q24</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Q26 Pourquoi ?</t>
+          <t>Q24 Quel est le principal point fort de cet appel ?</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -12723,37 +12723,37 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>HEURE_FIN</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Q25</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Heure fin</t>
+          <t>Q25 Quel est le principal irritant ou effort subi par le client ?</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Fin de l'évaluation</t>
+          <t>Synthèse qualitative</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>SCORE_TOTAL</t>
+          <t>Q26</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -12763,16 +12763,100 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Score total de l'appel</t>
+          <t>Q26 Le client devrait-il rappeler ou contacter un autre canal pour le même motif ?</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one oui_non</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
+        <is>
+          <t>Synthèse qualitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Q26_TXT</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Q26 Pourquoi ?</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Synthèse qualitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>HEURE_FIN</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Heure fin</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Fin de l'évaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>SCORE_TOTAL</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Score total de l'appel</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
         <is>
           <t>Fin de l'évaluation</t>
         </is>

--- a/correspondance_variables.xlsx
+++ b/correspondance_variables.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F425"/>
+  <dimension ref="A1:F422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REGION_ADMINISTRATIVE</t>
+          <t>OPERATEUR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Région administrative</t>
+          <t>Opérateur</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>select_one region</t>
+          <t>select_one reseau</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEPARTEMENT</t>
+          <t>DATE_INTERVIEW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Département</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>select_one departement</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -589,7 +589,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VILLE</t>
+          <t>JOUR_SEMAINE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Jour</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>select_one ville</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -617,7 +617,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPERATEUR</t>
+          <t>HEURE_DEBUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Opérateur</t>
+          <t>Heure début</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>select_one reseau</t>
+          <t>time</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DATE_INTERVIEW</t>
+          <t>LANGUE_ENQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Langue</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one langue</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -671,19 +671,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>JOUR_SEMAINE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>IDENT_CONSEILLER</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jour</t>
+          <t>Identification conseiller</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -699,24 +699,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HEURE_DEBUT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TRANCHE_HORAIRE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Heure début</t>
+          <t>Tranche horaire</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one tranche_horaire</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -727,37 +727,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LANGUE_ENQ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T_ATTENTE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Langue</t>
+          <t>Temps d'attente avant conseiller</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>select_one langue</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Identification de l'enquêteur</t>
+          <t>Mesures — valeurs observées</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IDENT_CONSEILLER</t>
+          <t>T_DUREE_APPEL</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -767,53 +767,53 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Identification conseiller</t>
+          <t>Durée totale de l'appel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Identification de l'enquêteur</t>
+          <t>Mesures — valeurs observées</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRANCHE_HORAIRE</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TEMPS_TOTAL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tranche horaire</t>
+          <t>Temps total en minutes passé en ligne avec le conseiller</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>select_one tranche_horaire</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Identification de l'enquêteur</t>
+          <t>Mesures — valeurs observées</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T_ATTENTE</t>
+          <t>NB_ATTENTES</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Temps d'attente avant conseiller</t>
+          <t>Nombre de mises en attente</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T_DUREE_APPEL</t>
+          <t>T_ATTENTES</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durée totale de l'appel</t>
+          <t>Durée cumulée des mises en attente</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -867,24 +867,24 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TEMPS_TOTAL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>NB_TRANSFERTS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Temps total en minutes passé en ligne avec le conseiller</t>
+          <t>Nombre de transferts</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -897,7 +897,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>NB_ATTENTES</t>
+          <t>RENVOI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nombre de mises en attente</t>
+          <t>Renvoi : le conseiller a-t-il orienté le client ailleurs qu'au téléphone ?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one renvoi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -925,7 +925,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T_ATTENTES</t>
+          <t>RENVOI_PRECISION</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durée cumulée des mises en attente</t>
+          <t>Préciser le canal, l'agence ou le point de vente indiqués</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -953,7 +953,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>NB_TRANSFERTS</t>
+          <t>ESCALADE</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nombre de transferts</t>
+          <t>Escalade : le dossier a-t-il été transmis à un autre service ou un rappel a-t-il été promis ?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one oui_non</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -979,37 +979,37 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>RENVOI</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SCENARIO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Renvoi : le conseiller a-t-il orienté le client ailleurs qu'au téléphone ?</t>
+          <t>Scénario</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>select_one renvoi</t>
+          <t>select_one scenario</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mesures — valeurs observées</t>
+          <t>Scénario joué</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RENVOI_PRECISION</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1019,25 +1019,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Préciser le canal, l'agence ou le point de vente indiqués</t>
+          <t xml:space="preserve">Q1 Le message d'accueil et les menus du serveur vocal vous ont-ils semblé clairs, compréhensibles et cohérents avec les </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>section A</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mesures — valeurs observées</t>
+          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ESCALADE</t>
+          <t>Q1_ALERTE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1047,53 +1051,53 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Escalade : le dossier a-t-il été transmis à un autre service ou un rappel a-t-il été promis ?</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>select_one oui_non</t>
+          <t>select_multiple alertes_a</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mesures — valeurs observées</t>
+          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SCENARIO</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Q1_COM</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>déduit — à valider</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scénario</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>select_one scenario</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Scénario joué</t>
+          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1103,7 +1107,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1 Le message d'accueil et les menus du serveur vocal vous ont-ils semblé clairs, compréhensibles et cohérents avec les </t>
+          <t>Q2 Le choix de langue vous a-t-il été proposé et a-t-il fonctionné correctement lorsqu'il était applicable à votre parco</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1125,7 +1129,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Q1_ALERTE</t>
+          <t>Q2_ALERTE</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1153,7 +1157,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Q1_COM</t>
+          <t>Q2_COM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1181,7 +1185,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Q2 Le choix de langue vous a-t-il été proposé et a-t-il fonctionné correctement lorsqu'il était applicable à votre parco</t>
+          <t>Q3 L'accès à un conseiller vous a-t-il semblé simple et fluide, sans erreur, ni boucle inutile ni confusion dans le parc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1213,7 +1217,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Q2_ALERTE</t>
+          <t>Q3_ALERTE</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1241,7 +1245,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Q2_COM</t>
+          <t>Q3_COM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1269,7 +1273,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>SCORE_A</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1279,19 +1283,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Q3 L'accès à un conseiller vous a-t-il semblé simple et fluide, sans erreur, ni boucle inutile ni confusion dans le parc</t>
+          <t>Score — Accessibilité &amp; serveur vocal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>section A</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
@@ -1301,7 +1301,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Q3_ALERTE</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1311,25 +1311,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Q4 Le conseiller vous a-t-il accueilli et s'est-il présenté de manière claire et professionnelle ?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>select_multiple alertes_a</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>section B</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
+          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Q3_COM</t>
+          <t>Q4_ALERTE</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1339,25 +1343,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_nc</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
+          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SCORE_A</t>
+          <t>Q4_COM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1367,25 +1371,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Score — Accessibilité &amp; serveur vocal</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A. ACCESSIBILITÉ &amp; SERVEUR VOCAL</t>
+          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1395,7 +1399,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Q4 Le conseiller vous a-t-il accueilli et s'est-il présenté de manière claire et professionnelle ?</t>
+          <t>Q5 Le ton du conseiller vous a-t-il semblé courtois, agréable et disponible, avec une personnalisation naturelle et appr</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1417,7 +1421,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Q4_ALERTE</t>
+          <t>Q5_ALERTE</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1445,7 +1449,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Q4_COM</t>
+          <t>Q5_COM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1473,7 +1477,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>SCORE_B</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1483,19 +1487,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Q5 Le ton du conseiller vous a-t-il semblé courtois, agréable et disponible, avec une personnalisation naturelle et appr</t>
+          <t>Score — Accueil &amp; posture du conseiller</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>section B</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
@@ -1505,7 +1505,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Q5_ALERTE</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1515,25 +1515,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Q6 Le conseiller vous a-t-il écouté attentivement et vous a-t-il laissé exposer votre besoin sans interruption inappropr</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>section C</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
+          <t>C. COMPRÉHENSION DU BESOIN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Q5_COM</t>
+          <t>Q6_ALERTE</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1543,25 +1547,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_c</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
+          <t>C. COMPRÉHENSION DU BESOIN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SCORE_B</t>
+          <t>Q6_COM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1571,25 +1575,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Score — Accueil &amp; posture du conseiller</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B. ACCUEIL &amp; POSTURE DU CONSEILLER</t>
+          <t>C. COMPRÉHENSION DU BESOIN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1599,7 +1603,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Q6 Le conseiller vous a-t-il écouté attentivement et vous a-t-il laissé exposer votre besoin sans interruption inappropr</t>
+          <t>Q7 Le conseiller a-t-il posé des questions pertinentes pour qualifier votre problème et obtenir uniquement les informati</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1621,7 +1625,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q6_ALERTE</t>
+          <t>Q7_ALERTE</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1649,7 +1653,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q6_COM</t>
+          <t>Q7_COM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1677,7 +1681,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1687,7 +1691,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Q7 Le conseiller a-t-il posé des questions pertinentes pour qualifier votre problème et obtenir uniquement les informati</t>
+          <t>Q8 Le conseiller a-t-il reformulé ou validé sa compréhension lorsque cela était utile, en évitant que vous répétiez inut</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1709,7 +1713,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Q7_ALERTE</t>
+          <t>Q8_ALERTE</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1737,7 +1741,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Q7_COM</t>
+          <t>Q8_COM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1765,7 +1769,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>SCORE_C</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1775,19 +1779,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Q8 Le conseiller a-t-il reformulé ou validé sa compréhension lorsque cela était utile, en évitant que vous répétiez inut</t>
+          <t>Score — Compréhension du besoin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>section C</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>C. COMPRÉHENSION DU BESOIN</t>
@@ -1797,7 +1797,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Q8_ALERTE</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1807,25 +1807,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t xml:space="preserve">Q9 Le conseiller a-t-il démontré une bonne maîtrise des offres, services, procédures et parcours liés au scénario testé </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>select_multiple alertes_c</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>section D</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C. COMPRÉHENSION DU BESOIN</t>
+          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Q8_COM</t>
+          <t>Q9_ALERTE</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1835,25 +1839,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_q9</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C. COMPRÉHENSION DU BESOIN</t>
+          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SCORE_C</t>
+          <t>Q9_COM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1863,25 +1867,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Score — Compréhension du besoin</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C. COMPRÉHENSION DU BESOIN</t>
+          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1891,7 +1895,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9 Le conseiller a-t-il démontré une bonne maîtrise des offres, services, procédures et parcours liés au scénario testé </t>
+          <t>Q10 La réponse fournie par le conseiller était-elle correcte, précise, cohérente et exempte d'informations contradictoir</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1913,7 +1917,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Q9_ALERTE</t>
+          <t>Q10_ALERTE</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1928,7 +1932,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>select_multiple alertes_q9</t>
+          <t>select_multiple alertes_q10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1941,7 +1945,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Q9_COM</t>
+          <t>Q10_COM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1969,7 +1973,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1979,7 +1983,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Q10 La réponse fournie par le conseiller était-elle correcte, précise, cohérente et exempte d'informations contradictoir</t>
+          <t>Q11 Les explications données vous ont-elles semblé simples, pédagogiques et adaptées, avec des étapes ou alternatives cl</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2001,7 +2005,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Q10_ALERTE</t>
+          <t>Q11_ALERTE</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2016,7 +2020,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>select_multiple alertes_q10</t>
+          <t>select_multiple alertes_q11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2029,7 +2033,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Q10_COM</t>
+          <t>Q11_COM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2057,7 +2061,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>SCORE_D</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2067,19 +2071,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Q11 Les explications données vous ont-elles semblé simples, pédagogiques et adaptées, avec des étapes ou alternatives cl</t>
+          <t>Score — Expertise &amp; exactitude de la réponse</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>section D</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
@@ -2089,7 +2089,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Q11_ALERTE</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2099,25 +2099,29 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Q12 La réponse apportée par le conseiller était-elle concrète, exploitable et vous a-t-elle permis d'avancer immédiateme</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>select_multiple alertes_q11</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>section E</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
+          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Q11_COM</t>
+          <t>Q12_ALERTE</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2127,25 +2131,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_nc</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
+          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SCORE_D</t>
+          <t>Q12_COM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2155,25 +2159,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Score — Expertise &amp; exactitude de la réponse</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>D. EXPERTISE &amp; EXACTITUDE DE LA RÉPONSE</t>
+          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2183,7 +2187,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Q12 La réponse apportée par le conseiller était-elle concrète, exploitable et vous a-t-elle permis d'avancer immédiateme</t>
+          <t>Q13 Votre besoin a-t-il été résolu dès le premier contact ou, lorsque la résolution immédiate était impossible, la meill</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2205,7 +2209,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Q12_ALERTE</t>
+          <t>Q13_ALERTE</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2233,7 +2237,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Q12_COM</t>
+          <t>Q13_COM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2261,7 +2265,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2271,7 +2275,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Q13 Votre besoin a-t-il été résolu dès le premier contact ou, lorsque la résolution immédiate était impossible, la meill</t>
+          <t>Q14 Le conseiller a-t-il pris ownership de votre demande, en évitant les transferts, renvois ou abandons de prise en cha</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2293,7 +2297,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Q13_ALERTE</t>
+          <t>Q14_ALERTE</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2321,7 +2325,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Q13_COM</t>
+          <t>Q14_COM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2349,7 +2353,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q15</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2359,7 +2363,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Q14 Le conseiller a-t-il pris ownership de votre demande, en évitant les transferts, renvois ou abandons de prise en cha</t>
+          <t>Q15 En cas d'escalade ou de renvoi en agence, le motif, les prochaines étapes, les pièces éventuelles et le délai annonc</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2381,7 +2385,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Q14_ALERTE</t>
+          <t>Q15_ALERTE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2409,7 +2413,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Q14_COM</t>
+          <t>Q15_COM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2437,7 +2441,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q16</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2447,7 +2451,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Q15 En cas d'escalade ou de renvoi en agence, le motif, les prochaines étapes, les pièces éventuelles et le délai annonc</t>
+          <t>Q16 Avant de clôturer l'appel, le conseiller a-t-il vérifié que la solution ou la suite du traitement était bien compris</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2469,7 +2473,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Q15_ALERTE</t>
+          <t>Q16_ALERTE</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -2497,7 +2501,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Q15_COM</t>
+          <t>Q16_COM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2525,7 +2529,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>SCORE_E</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2535,19 +2539,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Q16 Avant de clôturer l'appel, le conseiller a-t-il vérifié que la solution ou la suite du traitement était bien compris</t>
+          <t>Score — Résolution / FCR &amp; ownership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>section E</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
@@ -2557,7 +2557,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Q16_ALERTE</t>
+          <t>Q17</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2567,25 +2567,29 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Q17 Le nombre d'étapes, d'informations demandées et de manipulations imposées au client vous a-t-il semblé limité au str</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>section F</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
+          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q16_COM</t>
+          <t>Q17_ALERTE</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -2595,25 +2599,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_nc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
+          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SCORE_E</t>
+          <t>Q17_COM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2623,25 +2627,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Score — Résolution / FCR &amp; ownership</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>E. RÉSOLUTION / FCR &amp; OWNERSHIP</t>
+          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q18</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -2651,7 +2655,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Q17 Le nombre d'étapes, d'informations demandées et de manipulations imposées au client vous a-t-il semblé limité au str</t>
+          <t>Q18 Les mises en attente, transferts et changements de canal ont-ils été minimisés et, lorsqu'ils étaient nécessaires, e</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2673,7 +2677,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Q17_ALERTE</t>
+          <t>Q18_ALERTE</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2701,7 +2705,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Q17_COM</t>
+          <t>Q18_COM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -2729,7 +2733,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>SCORE_F</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2739,19 +2743,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Q18 Les mises en attente, transferts et changements de canal ont-ils été minimisés et, lorsqu'ils étaient nécessaires, e</t>
+          <t>Score — Effort client &amp; simplicité</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>section F</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
@@ -2761,7 +2761,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Q18_ALERTE</t>
+          <t>Q19</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -2771,25 +2771,29 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Q19 Le conseiller a-t-il reconnu de façon appropriée l'inconfort, l'urgence ou l'émotion que vous avez exprimés, notamme</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>section G</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
+          <t>G. EMPATHIE &amp; CONFIANCE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Q18_COM</t>
+          <t>Q19_ALERTE</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2799,25 +2803,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_nc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
+          <t>G. EMPATHIE &amp; CONFIANCE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SCORE_F</t>
+          <t>Q19_COM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -2827,25 +2831,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Score — Effort client &amp; simplicité</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>F. EFFORT CLIENT &amp; SIMPLICITÉ</t>
+          <t>G. EMPATHIE &amp; CONFIANCE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q20</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2855,7 +2859,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Q19 Le conseiller a-t-il reconnu de façon appropriée l'inconfort, l'urgence ou l'émotion que vous avez exprimés, notamme</t>
+          <t>Q20 L'attitude du conseiller, la transparence de ses explications et le respect de la confidentialité vous ont-ils inspi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2877,7 +2881,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Q19_ALERTE</t>
+          <t>Q20_ALERTE</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -2905,7 +2909,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Q19_COM</t>
+          <t>Q20_COM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2933,7 +2937,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>SCORE_G</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -2943,19 +2947,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Q20 L'attitude du conseiller, la transparence de ses explications et le respect de la confidentialité vous ont-ils inspi</t>
+          <t>Score — Empathie &amp; confiance</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>section G</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>G. EMPATHIE &amp; CONFIANCE</t>
@@ -2965,7 +2965,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Q20_ALERTE</t>
+          <t>Q21</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2975,25 +2975,29 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Q21 Le conseiller a-t-il récapitulé brièvement la solution ou les prochaines étapes, en vérifiant qu'aucun point essenti</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>section H</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>G. EMPATHIE &amp; CONFIANCE</t>
+          <t>H. CLÔTURE DE L'ENTRETIEN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Q20_COM</t>
+          <t>Q21_ALERTE</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -3003,25 +3007,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_nc</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>G. EMPATHIE &amp; CONFIANCE</t>
+          <t>H. CLÔTURE DE L'ENTRETIEN</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SCORE_G</t>
+          <t>Q21_COM</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3031,25 +3035,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Score — Empathie &amp; confiance</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>G. EMPATHIE &amp; CONFIANCE</t>
+          <t>H. CLÔTURE DE L'ENTRETIEN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q22</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -3059,7 +3063,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Q21 Le conseiller a-t-il récapitulé brièvement la solution ou les prochaines étapes, en vérifiant qu'aucun point essenti</t>
+          <t>Q22 La prise de congé du conseiller vous a-t-elle semblé courtoise, naturelle et professionnelle (remerciement ou souhai</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3081,7 +3085,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Q21_ALERTE</t>
+          <t>Q22_ALERTE</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3109,7 +3113,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Q21_COM</t>
+          <t>Q22_COM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -3137,7 +3141,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q23</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3147,7 +3151,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Q22 La prise de congé du conseiller vous a-t-elle semblé courtoise, naturelle et professionnelle (remerciement ou souhai</t>
+          <t>Q23 Le conseiller a-t-il informé le client qu'il recevra un sondage de satisfaction afin de partager son avis ?</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3169,7 +3173,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Q22_ALERTE</t>
+          <t>Q23_ALERTE</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -3197,7 +3201,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Q22_COM</t>
+          <t>Q23_COM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3225,7 +3229,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>SCORE_H</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -3235,19 +3239,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Q23 Le conseiller a-t-il informé le client qu'il recevra un sondage de satisfaction afin de partager son avis ?</t>
+          <t>Score — Clôture de l'entretien</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>section H</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>H. CLÔTURE DE L'ENTRETIEN</t>
@@ -3257,7 +3257,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Q23_ALERTE</t>
+          <t>S01_1</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3267,25 +3267,29 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>S01_1 Diagnostic — Le conseiller a-t-il identifié clairement la nature du problème et expliqué les causes possibles de l</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>select_one conformite</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>section I</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>H. CLÔTURE DE L'ENTRETIEN</t>
+          <t>I. MAÎTRISE DU SCÉNARIO</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Q23_COM</t>
+          <t>S01_1_ALERTE</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -3295,25 +3299,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple alertes_nc</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>H. CLÔTURE DE L'ENTRETIEN</t>
+          <t>I. MAÎTRISE DU SCÉNARIO</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SCORE_H</t>
+          <t>S01_1_COM</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3323,25 +3327,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Score — Clôture de l'entretien</t>
+          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>H. CLÔTURE DE L'ENTRETIEN</t>
+          <t>I. MAÎTRISE DU SCÉNARIO</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>S01_1</t>
+          <t>S01_2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -3351,7 +3355,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>S01_1 Diagnostic — Le conseiller a-t-il identifié clairement la nature du problème et expliqué les causes possibles de l</t>
+          <t>S01_2 Qualification — Le conseiller a-t-il posé des questions pertinentes pour qualifier le problème (forfait, téléphone</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3373,7 +3377,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>S01_1_ALERTE</t>
+          <t>S01_2_ALERTE</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -3401,7 +3405,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>S01_1_COM</t>
+          <t>S01_2_COM</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -3429,7 +3433,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>S01_2</t>
+          <t>S01_3</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -3439,7 +3443,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>S01_2 Qualification — Le conseiller a-t-il posé des questions pertinentes pour qualifier le problème (forfait, téléphone</t>
+          <t>S01_3 Vérification du contexte — Le conseiller a-t-il vérifié votre localisation, le type de terminal ou d'autres élémen</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3461,7 +3465,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>S01_2_ALERTE</t>
+          <t>S01_3_ALERTE</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -3489,7 +3493,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>S01_2_COM</t>
+          <t>S01_3_COM</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -3517,7 +3521,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>S01_3</t>
+          <t>S01_4</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -3527,7 +3531,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>S01_3 Vérification du contexte — Le conseiller a-t-il vérifié votre localisation, le type de terminal ou d'autres élémen</t>
+          <t xml:space="preserve">S01_4 Solution — Le conseiller a-t-il proposé une solution concrète et adaptée pour rétablir la qualité de la connexion </t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3549,7 +3553,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>S01_3_ALERTE</t>
+          <t>S01_4_ALERTE</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -3577,7 +3581,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>S01_3_COM</t>
+          <t>S01_4_COM</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -3605,7 +3609,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>S01_4</t>
+          <t>S01_5</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -3615,7 +3619,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">S01_4 Solution — Le conseiller a-t-il proposé une solution concrète et adaptée pour rétablir la qualité de la connexion </t>
+          <t>S01_5 Pédagogie — Le conseiller a-t-il expliqué les étapes de manière simple et compréhensible, vous permettant de repro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3637,7 +3641,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>S01_4_ALERTE</t>
+          <t>S01_5_ALERTE</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -3665,7 +3669,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>S01_4_COM</t>
+          <t>S01_5_COM</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -3693,7 +3697,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>S01_5</t>
+          <t>S02_1</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -3703,7 +3707,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>S01_5 Pédagogie — Le conseiller a-t-il expliqué les étapes de manière simple et compréhensible, vous permettant de repro</t>
+          <t>S02_1 Diagnostic des causes — Le conseiller a-t-il cherché à distinguer l'origine du problème (activation du forfait, co</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3725,7 +3729,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>S01_5_ALERTE</t>
+          <t>S02_1_ALERTE</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -3753,7 +3757,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>S01_5_COM</t>
+          <t>S02_1_COM</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -3781,7 +3785,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>S02_1</t>
+          <t>S02_2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -3791,7 +3795,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>S02_1 Diagnostic des causes — Le conseiller a-t-il cherché à distinguer l'origine du problème (activation du forfait, co</t>
+          <t>S02_2 Vérification de l'activation — Le conseiller a-t-il vérifié que le forfait avait bien été activé sur la ligne ?</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3813,7 +3817,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>S02_1_ALERTE</t>
+          <t>S02_2_ALERTE</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -3841,7 +3845,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>S02_1_COM</t>
+          <t>S02_2_COM</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -3869,7 +3873,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>S02_2</t>
+          <t>S02_3</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -3879,7 +3883,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>S02_2 Vérification de l'activation — Le conseiller a-t-il vérifié que le forfait avait bien été activé sur la ligne ?</t>
+          <t>S02_3 Vérification technique — Le conseiller a-t-il vérifié la configuration (APN, paramètres réseau) et la couverture r</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3901,7 +3905,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>S02_2_ALERTE</t>
+          <t>S02_3_ALERTE</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -3929,7 +3933,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>S02_2_COM</t>
+          <t>S02_3_COM</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -3957,7 +3961,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>S02_3</t>
+          <t>S02_4</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -3967,7 +3971,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>S02_3 Vérification technique — Le conseiller a-t-il vérifié la configuration (APN, paramètres réseau) et la couverture r</t>
+          <t>S02_4 Solution — Le conseiller a-t-il proposé une solution concrète pour rétablir la navigation ?</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3989,7 +3993,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>S02_3_ALERTE</t>
+          <t>S02_4_ALERTE</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -4017,7 +4021,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>S02_3_COM</t>
+          <t>S02_4_COM</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -4045,7 +4049,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>S02_4</t>
+          <t>S02_5</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -4055,7 +4059,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>S02_4 Solution — Le conseiller a-t-il proposé une solution concrète pour rétablir la navigation ?</t>
+          <t>S02_5 Alternative — Le conseiller a-t-il proposé une alternative en cas de non-résolution immédiate (remboursement, gest</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4077,7 +4081,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>S02_4_ALERTE</t>
+          <t>S02_5_ALERTE</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -4105,7 +4109,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>S02_4_COM</t>
+          <t>S02_5_COM</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -4133,7 +4137,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>S02_5</t>
+          <t>S03_1</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -4143,7 +4147,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>S02_5 Alternative — Le conseiller a-t-il proposé une alternative en cas de non-résolution immédiate (remboursement, gest</t>
+          <t>S03_1 Qualification du problème — Le conseiller a-t-il posé des questions pertinentes pour bien cerner la nature du prob</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4165,7 +4169,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>S02_5_ALERTE</t>
+          <t>S03_1_ALERTE</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -4193,7 +4197,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>S02_5_COM</t>
+          <t>S03_1_COM</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -4221,7 +4225,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>S03_1</t>
+          <t>S03_2</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -4231,7 +4235,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>S03_1 Qualification du problème — Le conseiller a-t-il posé des questions pertinentes pour bien cerner la nature du prob</t>
+          <t>S03_2 Localisation — Le conseiller a-t-il vérifié la zone géographique où le problème survient afin d'identifier un éven</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4253,7 +4257,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>S03_1_ALERTE</t>
+          <t>S03_2_ALERTE</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -4281,7 +4285,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>S03_1_COM</t>
+          <t>S03_2_COM</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -4309,7 +4313,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>S03_2</t>
+          <t>S03_3</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -4319,7 +4323,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>S03_2 Localisation — Le conseiller a-t-il vérifié la zone géographique où le problème survient afin d'identifier un éven</t>
+          <t>S03_3 Terminal / SIM — Le conseiller a-t-il demandé des précisions sur le type de téléphone, l'état de la carte SIM ou l</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4341,7 +4345,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>S03_2_ALERTE</t>
+          <t>S03_3_ALERTE</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -4369,7 +4373,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>S03_2_COM</t>
+          <t>S03_3_COM</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -4397,7 +4401,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>S03_3</t>
+          <t>S03_4</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -4407,7 +4411,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>S03_3 Terminal / SIM — Le conseiller a-t-il demandé des précisions sur le type de téléphone, l'état de la carte SIM ou l</t>
+          <t>S03_4 Incident réseau — Le conseiller a-t-il vérifié s'il existe un incident réseau connu pouvant expliquer les coupures</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4429,7 +4433,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>S03_3_ALERTE</t>
+          <t>S03_4_ALERTE</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -4457,7 +4461,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>S03_3_COM</t>
+          <t>S03_4_COM</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -4485,7 +4489,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>S03_4</t>
+          <t>S03_5</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -4495,7 +4499,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>S03_4 Incident réseau — Le conseiller a-t-il vérifié s'il existe un incident réseau connu pouvant expliquer les coupures</t>
+          <t xml:space="preserve">S03_5 Solution ou escalade — Le conseiller a-t-il proposé une solution concrète pour résoudre le problème ou, à défaut, </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4517,7 +4521,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>S03_4_ALERTE</t>
+          <t>S03_5_ALERTE</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -4545,7 +4549,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>S03_4_COM</t>
+          <t>S03_5_COM</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -4573,7 +4577,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>S03_5</t>
+          <t>S04_1</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -4583,7 +4587,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">S03_5 Solution ou escalade — Le conseiller a-t-il proposé une solution concrète pour résoudre le problème ou, à défaut, </t>
+          <t>S04_1 Vérification de la consommation — Le conseiller a-t-il vérifié la consommation réelle du forfait (historique, déta</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4605,7 +4609,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>S03_5_ALERTE</t>
+          <t>S04_1_ALERTE</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -4633,7 +4637,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>S03_5_COM</t>
+          <t>S04_1_COM</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -4661,7 +4665,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>S04_1</t>
+          <t>S04_2</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -4671,7 +4675,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>S04_1 Vérification de la consommation — Le conseiller a-t-il vérifié la consommation réelle du forfait (historique, déta</t>
+          <t>S04_2 Transparence — Le conseiller a-t-il expliqué clairement au client comment son forfait a été consommé aussi rapidem</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4693,7 +4697,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>S04_1_ALERTE</t>
+          <t>S04_2_ALERTE</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -4721,7 +4725,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>S04_1_COM</t>
+          <t>S04_2_COM</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -4749,7 +4753,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>S04_2</t>
+          <t>S04_3</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -4759,7 +4763,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>S04_2 Transparence — Le conseiller a-t-il expliqué clairement au client comment son forfait a été consommé aussi rapidem</t>
+          <t>S04_3 Vérification du disponible — Le conseiller a-t-il vérifié s'il existait un reliquat, un bonus ou un forfait complé</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4781,7 +4785,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>S04_2_ALERTE</t>
+          <t>S04_3_ALERTE</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -4809,7 +4813,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>S04_2_COM</t>
+          <t>S04_3_COM</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -4837,7 +4841,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>S04_3</t>
+          <t>S04_4</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -4847,7 +4851,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>S04_3 Vérification du disponible — Le conseiller a-t-il vérifié s'il existait un reliquat, un bonus ou un forfait complé</t>
+          <t>S04_4 Conseils de maîtrise — Le conseiller a-t-il donné des conseils pratiques pour mieux maîtriser sa consommation à l'</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4869,7 +4873,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>S04_3_ALERTE</t>
+          <t>S04_4_ALERTE</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -4897,7 +4901,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>S04_3_COM</t>
+          <t>S04_4_COM</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -4925,7 +4929,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>S04_4</t>
+          <t>S05_1</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -4935,7 +4939,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>S04_4 Conseils de maîtrise — Le conseiller a-t-il donné des conseils pratiques pour mieux maîtriser sa consommation à l'</t>
+          <t xml:space="preserve">S05_1 Investigation — Le conseiller a-t-il mené une investigation rigoureuse pour identifier l'origine du débit (détail </t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4957,7 +4961,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>S04_4_ALERTE</t>
+          <t>S05_1_ALERTE</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -4985,7 +4989,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>S04_4_COM</t>
+          <t>S05_1_COM</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -5013,7 +5017,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>S05_1</t>
+          <t>S05_2</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -5023,7 +5027,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">S05_1 Investigation — Le conseiller a-t-il mené une investigation rigoureuse pour identifier l'origine du débit (détail </t>
+          <t>S05_2 Identification des postes de débit — Le conseiller a-t-il vérifié les différentes sources possibles (data hors for</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5045,7 +5049,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>S05_1_ALERTE</t>
+          <t>S05_2_ALERTE</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -5073,7 +5077,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>S05_1_COM</t>
+          <t>S05_2_COM</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -5101,7 +5105,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>S05_2</t>
+          <t>S05_3</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -5111,7 +5115,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>S05_2 Identification des postes de débit — Le conseiller a-t-il vérifié les différentes sources possibles (data hors for</t>
+          <t>S05_3 Exactitude — Le conseiller a-t-il fourni des informations exactes et vérifiées sur les montants et la nature des d</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5133,7 +5137,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>S05_2_ALERTE</t>
+          <t>S05_3_ALERTE</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -5161,7 +5165,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>S05_2_COM</t>
+          <t>S05_3_COM</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -5189,7 +5193,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>S05_3</t>
+          <t>S05_4</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -5199,7 +5203,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>S05_3 Exactitude — Le conseiller a-t-il fourni des informations exactes et vérifiées sur les montants et la nature des d</t>
+          <t>S05_4 Explication claire — Le conseiller a-t-il expliqué la situation de façon claire et compréhensible pour le client ?</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5221,7 +5225,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>S05_3_ALERTE</t>
+          <t>S05_4_ALERTE</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -5249,7 +5253,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>S05_3_COM</t>
+          <t>S05_4_COM</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -5277,7 +5281,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>S05_4</t>
+          <t>S06_1</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -5287,7 +5291,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>S05_4 Explication claire — Le conseiller a-t-il expliqué la situation de façon claire et compréhensible pour le client ?</t>
+          <t>S06_1 Identification du service — Le conseiller a-t-il identifié précisément le service VAS concerné et son mode de sous</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5309,7 +5313,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>S05_4_ALERTE</t>
+          <t>S06_1_ALERTE</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -5337,7 +5341,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>S05_4_COM</t>
+          <t>S06_1_COM</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -5365,7 +5369,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>S06_1</t>
+          <t>S06_2</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -5375,7 +5379,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>S06_1 Identification du service — Le conseiller a-t-il identifié précisément le service VAS concerné et son mode de sous</t>
+          <t>S06_2 Désactivation — Le conseiller a-t-il procédé ou proposé la désactivation immédiate du service ?</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5397,7 +5401,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>S06_1_ALERTE</t>
+          <t>S06_2_ALERTE</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -5425,7 +5429,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>S06_1_COM</t>
+          <t>S06_2_COM</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -5453,7 +5457,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>S06_2</t>
+          <t>S06_3</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -5463,7 +5467,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>S06_2 Désactivation — Le conseiller a-t-il procédé ou proposé la désactivation immédiate du service ?</t>
+          <t>S06_3 Procédure de contestation / remboursement — Le conseiller a-t-il expliqué la procédure de contestation et, si appl</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5485,7 +5489,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>S06_2_ALERTE</t>
+          <t>S06_3_ALERTE</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -5513,7 +5517,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>S06_2_COM</t>
+          <t>S06_3_COM</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -5541,7 +5545,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>S06_3</t>
+          <t>S06_4</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -5551,7 +5555,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>S06_3 Procédure de contestation / remboursement — Le conseiller a-t-il expliqué la procédure de contestation et, si appl</t>
+          <t>S06_4 Rassurance — Le conseiller a-t-il rassuré le client et vérifié qu'aucune autre souscription non désirée n'était ac</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5573,7 +5577,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>S06_3_ALERTE</t>
+          <t>S06_4_ALERTE</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -5601,7 +5605,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>S06_3_COM</t>
+          <t>S06_4_COM</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -5629,7 +5633,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>S06_4</t>
+          <t>S07_1</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -5639,7 +5643,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>S06_4 Rassurance — Le conseiller a-t-il rassuré le client et vérifié qu'aucune autre souscription non désirée n'était ac</t>
+          <t>S07_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause de l'échec de la transaction (solde, canal utilisé</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5661,7 +5665,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>S06_4_ALERTE</t>
+          <t>S07_1_ALERTE</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -5689,7 +5693,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>S06_4_COM</t>
+          <t>S07_1_COM</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -5717,7 +5721,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>S07_1</t>
+          <t>S07_2</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -5727,7 +5731,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>S07_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause de l'échec de la transaction (solde, canal utilisé</t>
+          <t>S07_2 Connaissance du parcours — Le conseiller a-t-il démontré une bonne connaissance des différents canaux d'achat (USS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5749,7 +5753,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>S07_1_ALERTE</t>
+          <t>S07_2_ALERTE</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -5777,7 +5781,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>S07_1_COM</t>
+          <t>S07_2_COM</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -5805,7 +5809,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>S07_2</t>
+          <t>S07_3</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -5815,7 +5819,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>S07_2 Connaissance du parcours — Le conseiller a-t-il démontré une bonne connaissance des différents canaux d'achat (USS</t>
+          <t>S07_3 Alternatives proposées — Le conseiller a-t-il proposé un canal alternatif pour finaliser l'achat ?</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5837,7 +5841,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>S07_2_ALERTE</t>
+          <t>S07_3_ALERTE</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -5865,7 +5869,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>S07_2_COM</t>
+          <t>S07_3_COM</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -5893,7 +5897,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>S07_3</t>
+          <t>S07_4</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -5903,7 +5907,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>S07_3 Alternatives proposées — Le conseiller a-t-il proposé un canal alternatif pour finaliser l'achat ?</t>
+          <t>S07_4 Accompagnement — Le conseiller a-t-il accompagné le client pas à pas jusqu'à la résolution du problème ?</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5925,7 +5929,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>S07_3_ALERTE</t>
+          <t>S07_4_ALERTE</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -5953,7 +5957,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>S07_3_COM</t>
+          <t>S07_4_COM</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -5981,7 +5985,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>S07_4</t>
+          <t>S08_1</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -5991,7 +5995,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>S07_4 Accompagnement — Le conseiller a-t-il accompagné le client pas à pas jusqu'à la résolution du problème ?</t>
+          <t>S08_1 Assistance digitale — Le conseiller a-t-il apporté une assistance technique adaptée au problème de connexion ?</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6013,7 +6017,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>S07_4_ALERTE</t>
+          <t>S08_1_ALERTE</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -6041,7 +6045,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>S07_4_COM</t>
+          <t>S08_1_COM</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -6069,7 +6073,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>S08_1</t>
+          <t>S08_2</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -6079,7 +6083,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>S08_1 Assistance digitale — Le conseiller a-t-il apporté une assistance technique adaptée au problème de connexion ?</t>
+          <t>S08_2 Étapes simples — Le conseiller a-t-il expliqué les étapes de résolution de manière simple et progressive ?</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6101,7 +6105,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>S08_1_ALERTE</t>
+          <t>S08_2_ALERTE</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -6129,7 +6133,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>S08_1_COM</t>
+          <t>S08_2_COM</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -6157,7 +6161,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>S08_2</t>
+          <t>S08_3</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -6167,7 +6171,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>S08_2 Étapes simples — Le conseiller a-t-il expliqué les étapes de résolution de manière simple et progressive ?</t>
+          <t>S08_3 Récupération d'accès — Le conseiller a-t-il aidé le client à récupérer l'accès à son compte (mot de passe, identif</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6189,7 +6193,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>S08_2_ALERTE</t>
+          <t>S08_3_ALERTE</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -6217,7 +6221,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>S08_2_COM</t>
+          <t>S08_3_COM</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -6245,7 +6249,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>S08_3</t>
+          <t>S08_4</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -6255,7 +6259,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>S08_3 Récupération d'accès — Le conseiller a-t-il aidé le client à récupérer l'accès à son compte (mot de passe, identif</t>
+          <t>S08_4 Alternative — Le conseiller a-t-il proposé une alternative en cas d'indisponibilité prolongée de l'application (US</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -6277,7 +6281,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>S08_3_ALERTE</t>
+          <t>S08_4_ALERTE</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -6305,7 +6309,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>S08_3_COM</t>
+          <t>S08_4_COM</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -6333,7 +6337,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>S08_4</t>
+          <t>S09_1</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -6343,7 +6347,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>S08_4 Alternative — Le conseiller a-t-il proposé une alternative en cas d'indisponibilité prolongée de l'application (US</t>
+          <t>S09_1 Découverte du besoin — Le conseiller a-t-il posé des questions pour bien cerner les besoins et habitudes de consom</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6365,7 +6369,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>S08_4_ALERTE</t>
+          <t>S09_1_ALERTE</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -6393,7 +6397,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>S08_4_COM</t>
+          <t>S09_1_COM</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -6421,7 +6425,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>S09_1</t>
+          <t>S09_2</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -6431,7 +6435,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>S09_1 Découverte du besoin — Le conseiller a-t-il posé des questions pour bien cerner les besoins et habitudes de consom</t>
+          <t>S09_2 Personnalisation — Le conseiller a-t-il adapté sa réponse au profil et au budget exprimés par le client ?</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -6453,7 +6457,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>S09_1_ALERTE</t>
+          <t>S09_2_ALERTE</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -6481,7 +6485,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>S09_1_COM</t>
+          <t>S09_2_COM</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -6509,7 +6513,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>S09_2</t>
+          <t>S09_3</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -6519,7 +6523,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>S09_2 Personnalisation — Le conseiller a-t-il adapté sa réponse au profil et au budget exprimés par le client ?</t>
+          <t>S09_3 Connaissance du catalogue — Le conseiller a-t-il démontré une bonne connaissance des offres disponibles ?</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6541,7 +6545,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>S09_2_ALERTE</t>
+          <t>S09_3_ALERTE</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -6569,7 +6573,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>S09_2_COM</t>
+          <t>S09_3_COM</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -6597,7 +6601,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>S09_3</t>
+          <t>S09_4</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -6607,7 +6611,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>S09_3 Connaissance du catalogue — Le conseiller a-t-il démontré une bonne connaissance des offres disponibles ?</t>
+          <t xml:space="preserve">S09_4 Pertinence de la recommandation — Le conseiller a-t-il proposé un forfait réellement adapté aux besoins exprimés, </t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6629,7 +6633,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>S09_3_ALERTE</t>
+          <t>S09_4_ALERTE</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -6657,7 +6661,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>S09_3_COM</t>
+          <t>S09_4_COM</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -6685,7 +6689,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>S09_4</t>
+          <t>S10_1</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -6695,7 +6699,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">S09_4 Pertinence de la recommandation — Le conseiller a-t-il proposé un forfait réellement adapté aux besoins exprimés, </t>
+          <t>S10_1 Compréhension de l'usage — Le conseiller a-t-il bien compris les habitudes de consommation actuelles du client ?</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6717,7 +6721,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>S09_4_ALERTE</t>
+          <t>S10_1_ALERTE</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -6745,7 +6749,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>S09_4_COM</t>
+          <t>S10_1_COM</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -6773,7 +6777,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>S10_1</t>
+          <t>S10_2</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -6783,7 +6787,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>S10_1 Compréhension de l'usage — Le conseiller a-t-il bien compris les habitudes de consommation actuelles du client ?</t>
+          <t>S10_2 Présentation des options — Le conseiller a-t-il présenté les différentes options disponibles correspondant à la de</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6805,7 +6809,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>S10_1_ALERTE</t>
+          <t>S10_2_ALERTE</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -6833,7 +6837,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>S10_1_COM</t>
+          <t>S10_2_COM</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -6861,7 +6865,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>S10_2</t>
+          <t>S10_3</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -6871,7 +6875,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>S10_2 Présentation des options — Le conseiller a-t-il présenté les différentes options disponibles correspondant à la de</t>
+          <t>S10_3 Prise en compte des contraintes — Le conseiller a-t-il tenu compte des contraintes du client (engagement, coût, co</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6893,7 +6897,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>S10_2_ALERTE</t>
+          <t>S10_3_ALERTE</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -6921,7 +6925,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>S10_2_COM</t>
+          <t>S10_3_COM</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -6949,7 +6953,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>S10_3</t>
+          <t>S10_4</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -6959,7 +6963,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>S10_3 Prise en compte des contraintes — Le conseiller a-t-il tenu compte des contraintes du client (engagement, coût, co</t>
+          <t>S10_4 Conseil adapté — Le conseiller a-t-il proposé une offre réellement adaptée à la demande du client ?</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6981,7 +6985,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>S10_3_ALERTE</t>
+          <t>S10_4_ALERTE</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -7009,7 +7013,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>S10_3_COM</t>
+          <t>S10_4_COM</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -7037,7 +7041,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>S10_4</t>
+          <t>S10_5</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -7047,7 +7051,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>S10_4 Conseil adapté — Le conseiller a-t-il proposé une offre réellement adaptée à la demande du client ?</t>
+          <t>S10_5 Absence de vente forcée — Le conseiller a-t-il respecté le choix du client sans forcer une offre plus chère ou non</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -7069,7 +7073,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>S10_4_ALERTE</t>
+          <t>S10_5_ALERTE</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -7097,7 +7101,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>S10_4_COM</t>
+          <t>S10_5_COM</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -7125,7 +7129,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>S10_5</t>
+          <t>S11_1</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -7135,7 +7139,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>S10_5 Absence de vente forcée — Le conseiller a-t-il respecté le choix du client sans forcer une offre plus chère ou non</t>
+          <t>S11_1 Authentification — Le conseiller a-t-il procédé à une vérification d'identité conforme avant de communiquer le cod</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -7157,7 +7161,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>S10_5_ALERTE</t>
+          <t>S11_1_ALERTE</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -7185,7 +7189,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>S10_5_COM</t>
+          <t>S11_1_COM</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -7213,7 +7217,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>S11_1</t>
+          <t>S11_2</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -7223,7 +7227,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>S11_1 Authentification — Le conseiller a-t-il procédé à une vérification d'identité conforme avant de communiquer le cod</t>
+          <t>S11_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité tout au long de l'échange ?</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7245,7 +7249,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>S11_1_ALERTE</t>
+          <t>S11_2_ALERTE</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -7273,7 +7277,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>S11_1_COM</t>
+          <t>S11_2_COM</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -7301,7 +7305,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>S11_2</t>
+          <t>S11_3</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -7311,7 +7315,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>S11_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité tout au long de l'échange ?</t>
+          <t>S11_3 Rapidité de résolution — Le conseiller a-t-il résolu la situation rapidement et efficacement ?</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -7333,7 +7337,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>S11_2_ALERTE</t>
+          <t>S11_3_ALERTE</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -7361,7 +7365,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>S11_2_COM</t>
+          <t>S11_3_COM</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -7389,7 +7393,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>S11_3</t>
+          <t>S11_4</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -7399,7 +7403,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>S11_3 Rapidité de résolution — Le conseiller a-t-il résolu la situation rapidement et efficacement ?</t>
+          <t>S11_4 Pédagogie — Le conseiller a-t-il expliqué au client comment éviter ce type de blocage à l'avenir ?</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -7421,7 +7425,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>S11_3_ALERTE</t>
+          <t>S11_4_ALERTE</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -7449,7 +7453,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>S11_3_COM</t>
+          <t>S11_4_COM</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -7477,7 +7481,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>S11_4</t>
+          <t>S12_1</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -7487,7 +7491,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>S11_4 Pédagogie — Le conseiller a-t-il expliqué au client comment éviter ce type de blocage à l'avenir ?</t>
+          <t>S12_1 Priorisation de la sécurité — Le conseiller a-t-il traité la demande en priorité, avec le sérieux requis par la si</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -7509,7 +7513,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>S11_4_ALERTE</t>
+          <t>S12_1_ALERTE</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -7537,7 +7541,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>S11_4_COM</t>
+          <t>S12_1_COM</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -7565,7 +7569,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>S12_1</t>
+          <t>S12_2</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -7575,7 +7579,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>S12_1 Priorisation de la sécurité — Le conseiller a-t-il traité la demande en priorité, avec le sérieux requis par la si</t>
+          <t>S12_2 Blocage / protection — Le conseiller a-t-il procédé ou guidé le client vers le blocage immédiat de la ligne ?</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7597,7 +7601,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>S12_1_ALERTE</t>
+          <t>S12_2_ALERTE</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -7625,7 +7629,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>S12_1_COM</t>
+          <t>S12_2_COM</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -7653,7 +7657,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>S12_2</t>
+          <t>S12_3</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -7663,7 +7667,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>S12_2 Blocage / protection — Le conseiller a-t-il procédé ou guidé le client vers le blocage immédiat de la ligne ?</t>
+          <t>S12_3 Authentification — Le conseiller a-t-il vérifié l'identité du client selon la procédure requise avant toute action</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7685,7 +7689,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>S12_2_ALERTE</t>
+          <t>S12_3_ALERTE</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -7713,7 +7717,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>S12_2_COM</t>
+          <t>S12_3_COM</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -7741,7 +7745,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>S12_3</t>
+          <t>S12_4</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -7751,7 +7755,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>S12_3 Authentification — Le conseiller a-t-il vérifié l'identité du client selon la procédure requise avant toute action</t>
+          <t>S12_4 Procédure de remplacement — Le conseiller a-t-il expliqué clairement la procédure pour obtenir une nouvelle SIM ?</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7773,7 +7777,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>S12_3_ALERTE</t>
+          <t>S12_4_ALERTE</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -7801,7 +7805,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>S12_3_COM</t>
+          <t>S12_4_COM</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -7829,7 +7833,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>S12_4</t>
+          <t>S13_1</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -7839,7 +7843,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>S12_4 Procédure de remplacement — Le conseiller a-t-il expliqué clairement la procédure pour obtenir une nouvelle SIM ?</t>
+          <t>S13_1 Maîtrise KYC — Le conseiller a-t-il fait preuve d'une bonne maîtrise des règles d'identification (KYC) applicables</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7861,7 +7865,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>S12_4_ALERTE</t>
+          <t>S13_1_ALERTE</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -7889,7 +7893,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>S12_4_COM</t>
+          <t>S13_1_COM</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -7917,7 +7921,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>S13_1</t>
+          <t>S13_2</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -7927,7 +7931,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>S13_1 Maîtrise KYC — Le conseiller a-t-il fait preuve d'une bonne maîtrise des règles d'identification (KYC) applicables</t>
+          <t>S13_2 Clarté de la procédure — Le conseiller a-t-il expliqué clairement la procédure à suivre pour régulariser la situat</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7949,7 +7953,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>S13_1_ALERTE</t>
+          <t>S13_2_ALERTE</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -7977,7 +7981,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>S13_1_COM</t>
+          <t>S13_2_COM</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -8005,7 +8009,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>S13_2</t>
+          <t>S13_3</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -8015,7 +8019,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>S13_2 Clarté de la procédure — Le conseiller a-t-il expliqué clairement la procédure à suivre pour régulariser la situat</t>
+          <t>S13_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives nécessaires et le canal à utiliser ?</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8037,7 +8041,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>S13_2_ALERTE</t>
+          <t>S13_3_ALERTE</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -8065,7 +8069,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>S13_2_COM</t>
+          <t>S13_3_COM</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -8093,7 +8097,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>S13_3</t>
+          <t>S13_4</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -8103,7 +8107,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>S13_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives nécessaires et le canal à utiliser ?</t>
+          <t xml:space="preserve">S13_4 Minimisation de l'effort — Le conseiller a-t-il proposé la solution la plus simple et la moins contraignante pour </t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -8125,7 +8129,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>S13_3_ALERTE</t>
+          <t>S13_4_ALERTE</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -8153,7 +8157,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>S13_3_COM</t>
+          <t>S13_4_COM</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -8181,7 +8185,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>S13_4</t>
+          <t>S14_1</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -8191,7 +8195,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">S13_4 Minimisation de l'effort — Le conseiller a-t-il proposé la solution la plus simple et la moins contraignante pour </t>
+          <t>S14_1 Consultation de l'historique — Le conseiller a-t-il consulté l'historique des échanges précédents avant de répondr</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -8213,7 +8217,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>S13_4_ALERTE</t>
+          <t>S14_1_ALERTE</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -8241,7 +8245,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>S13_4_COM</t>
+          <t>S14_1_COM</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -8269,7 +8273,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>S14_1</t>
+          <t>S14_2</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -8279,7 +8283,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>S14_1 Consultation de l'historique — Le conseiller a-t-il consulté l'historique des échanges précédents avant de répondr</t>
+          <t>S14_2 Reconnaissance de la récurrence — Le conseiller a-t-il reconnu explicitement le caractère récurrent du problème ?</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -8301,7 +8305,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>S14_1_ALERTE</t>
+          <t>S14_2_ALERTE</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -8329,7 +8333,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>S14_1_COM</t>
+          <t>S14_2_COM</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -8357,7 +8361,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>S14_2</t>
+          <t>S14_3</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -8367,7 +8371,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>S14_2 Reconnaissance de la récurrence — Le conseiller a-t-il reconnu explicitement le caractère récurrent du problème ?</t>
+          <t>S14_3 Ownership — Le conseiller a-t-il pris en charge la demande sans renvoyer la responsabilité au client ?</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -8389,7 +8393,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>S14_2_ALERTE</t>
+          <t>S14_3_ALERTE</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -8417,7 +8421,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>S14_2_COM</t>
+          <t>S14_3_COM</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -8445,7 +8449,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>S14_3</t>
+          <t>S14_4</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -8455,7 +8459,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>S14_3 Ownership — Le conseiller a-t-il pris en charge la demande sans renvoyer la responsabilité au client ?</t>
+          <t>S14_4 Escalade appropriée — Le conseiller a-t-il procédé à une escalade adaptée si nécessaire ?</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -8477,7 +8481,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>S14_3_ALERTE</t>
+          <t>S14_4_ALERTE</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -8505,7 +8509,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>S14_3_COM</t>
+          <t>S14_4_COM</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -8533,7 +8537,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>S14_4</t>
+          <t>S14_5</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -8543,7 +8547,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>S14_4 Escalade appropriée — Le conseiller a-t-il procédé à une escalade adaptée si nécessaire ?</t>
+          <t>S14_5 Délai / next step — Le conseiller a-t-il communiqué un délai clair et une prochaine étape précise ?</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -8565,7 +8569,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>S14_4_ALERTE</t>
+          <t>S14_5_ALERTE</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -8593,7 +8597,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>S14_4_COM</t>
+          <t>S14_5_COM</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -8621,7 +8625,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>S14_5</t>
+          <t>S15_1</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -8631,7 +8635,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>S14_5 Délai / next step — Le conseiller a-t-il communiqué un délai clair et une prochaine étape précise ?</t>
+          <t>S15_1 Écoute émotionnelle — Le conseiller a-t-il su écouter le mécontentement du client sans l'interrompre ni se justifi</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8653,7 +8657,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>S14_5_ALERTE</t>
+          <t>S15_1_ALERTE</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -8681,7 +8685,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>S14_5_COM</t>
+          <t>S15_1_COM</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -8709,7 +8713,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>S15_1</t>
+          <t>S15_2</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -8719,7 +8723,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>S15_1 Écoute émotionnelle — Le conseiller a-t-il su écouter le mécontentement du client sans l'interrompre ni se justifi</t>
+          <t>S15_2 Désescalade — Le conseiller a-t-il su désamorcer la tension par son attitude et son discours ?</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8741,7 +8745,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>S15_1_ALERTE</t>
+          <t>S15_2_ALERTE</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -8769,7 +8773,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>S15_1_COM</t>
+          <t>S15_2_COM</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -8797,7 +8801,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>S15_2</t>
+          <t>S15_3</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -8807,7 +8811,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S15_2 Désescalade — Le conseiller a-t-il su désamorcer la tension par son attitude et son discours ?</t>
+          <t>S15_3 Empathie — Le conseiller a-t-il exprimé de l'empathie envers la situation vécue par le client ?</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8829,7 +8833,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>S15_2_ALERTE</t>
+          <t>S15_3_ALERTE</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -8857,7 +8861,7 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>S15_2_COM</t>
+          <t>S15_3_COM</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -8885,7 +8889,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>S15_3</t>
+          <t>S15_4</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -8895,7 +8899,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>S15_3 Empathie — Le conseiller a-t-il exprimé de l'empathie envers la situation vécue par le client ?</t>
+          <t>S15_4 Reprise en main — Le conseiller a-t-il repris le contrôle de l'échange de façon professionnelle et rassurante ?</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8917,7 +8921,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>S15_3_ALERTE</t>
+          <t>S15_4_ALERTE</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -8945,7 +8949,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>S15_3_COM</t>
+          <t>S15_4_COM</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -8973,7 +8977,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>S15_4</t>
+          <t>S15_5</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -8983,7 +8987,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>S15_4 Reprise en main — Le conseiller a-t-il repris le contrôle de l'échange de façon professionnelle et rassurante ?</t>
+          <t>S15_5 Recherche de solution — Le conseiller a-t-il orienté l'échange vers une recherche concrète de solution ?</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9005,7 +9009,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>S15_4_ALERTE</t>
+          <t>S15_5_ALERTE</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -9033,7 +9037,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>S15_4_COM</t>
+          <t>S15_5_COM</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -9061,7 +9065,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>S15_5</t>
+          <t>S16_1</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -9071,7 +9075,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>S15_5 Recherche de solution — Le conseiller a-t-il orienté l'échange vers une recherche concrète de solution ?</t>
+          <t>S16_1 Rapidité — Le conseiller a-t-il répondu rapidement à la demande ?</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9093,7 +9097,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>S15_5_ALERTE</t>
+          <t>S16_1_ALERTE</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -9121,7 +9125,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>S15_5_COM</t>
+          <t>S16_1_COM</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -9149,7 +9153,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>S16_1</t>
+          <t>S16_2</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -9159,7 +9163,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>S16_1 Rapidité — Le conseiller a-t-il répondu rapidement à la demande ?</t>
+          <t>S16_2 Exactitude — L'information tarifaire communiquée était-elle exacte ?</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -9181,7 +9185,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>S16_1_ALERTE</t>
+          <t>S16_2_ALERTE</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -9209,7 +9213,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>S16_1_COM</t>
+          <t>S16_2_COM</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -9237,7 +9241,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>S16_2</t>
+          <t>S16_3</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -9247,7 +9251,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>S16_2 Exactitude — L'information tarifaire communiquée était-elle exacte ?</t>
+          <t>S16_3 Simplicité — La réponse a-t-elle été formulée de façon simple et directement compréhensible ?</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -9269,7 +9273,7 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>S16_2_ALERTE</t>
+          <t>S16_3_ALERTE</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -9297,7 +9301,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>S16_2_COM</t>
+          <t>S16_3_COM</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -9325,7 +9329,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>S16_3</t>
+          <t>S16_4</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -9335,7 +9339,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S16_3 Simplicité — La réponse a-t-elle été formulée de façon simple et directement compréhensible ?</t>
+          <t>S16_4 Absence d'informations inutiles — Le conseiller a-t-il évité de noyer la réponse dans des informations non demandé</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -9357,7 +9361,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>S16_3_ALERTE</t>
+          <t>S16_4_ALERTE</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -9385,7 +9389,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>S16_3_COM</t>
+          <t>S16_4_COM</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -9413,7 +9417,7 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>S16_4</t>
+          <t>S17_1</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -9423,7 +9427,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>S16_4 Absence d'informations inutiles — Le conseiller a-t-il évité de noyer la réponse dans des informations non demandé</t>
+          <t>S17_1 Maîtrise du roaming — Le conseiller a-t-il démontré une bonne connaissance des conditions d'utilisation à l'étrang</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -9445,7 +9449,7 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>S16_4_ALERTE</t>
+          <t>S17_1_ALERTE</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -9473,7 +9477,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>S16_4_COM</t>
+          <t>S17_1_COM</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -9501,7 +9505,7 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>S17_1</t>
+          <t>S17_2</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -9511,7 +9515,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>S17_1 Maîtrise du roaming — Le conseiller a-t-il démontré une bonne connaissance des conditions d'utilisation à l'étrang</t>
+          <t>S17_2 Conditions d'activation — Le conseiller a-t-il expliqué les éventuelles conditions d'activation du roaming ?</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -9533,7 +9537,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>S17_1_ALERTE</t>
+          <t>S17_2_ALERTE</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -9561,7 +9565,7 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>S17_1_COM</t>
+          <t>S17_2_COM</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -9589,7 +9593,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>S17_2</t>
+          <t>S17_3</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -9599,7 +9603,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>S17_2 Conditions d'activation — Le conseiller a-t-il expliqué les éventuelles conditions d'activation du roaming ?</t>
+          <t>S17_3 Tarification — Le conseiller a-t-il communiqué une information tarifaire claire et exacte pour la destination conc</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -9621,7 +9625,7 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>S17_2_ALERTE</t>
+          <t>S17_3_ALERTE</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -9649,7 +9653,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>S17_2_COM</t>
+          <t>S17_3_COM</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -9677,7 +9681,7 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>S17_3</t>
+          <t>S17_4</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -9687,7 +9691,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>S17_3 Tarification — Le conseiller a-t-il communiqué une information tarifaire claire et exacte pour la destination conc</t>
+          <t>S17_4 Prévention du hors-forfait — Le conseiller a-t-il alerté le client sur les risques de hors-forfait et les moyens d</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -9709,7 +9713,7 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>S17_3_ALERTE</t>
+          <t>S17_4_ALERTE</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -9737,7 +9741,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>S17_3_COM</t>
+          <t>S17_4_COM</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -9765,7 +9769,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>S17_4</t>
+          <t>S17_5</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -9775,7 +9779,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>S17_4 Prévention du hors-forfait — Le conseiller a-t-il alerté le client sur les risques de hors-forfait et les moyens d</t>
+          <t>S17_5 Conseil — Le conseiller a-t-il proposé une offre ou un conseil adapté au voyage du client ?</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9797,7 +9801,7 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>S17_4_ALERTE</t>
+          <t>S17_5_ALERTE</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -9825,7 +9829,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>S17_4_COM</t>
+          <t>S17_5_COM</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -9853,7 +9857,7 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>S17_5</t>
+          <t>S18_1</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -9863,7 +9867,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>S17_5 Conseil — Le conseiller a-t-il proposé une offre ou un conseil adapté au voyage du client ?</t>
+          <t>S18_1 Connaissance des canaux — Le conseiller a-t-il démontré une bonne connaissance des procédures via USSD et/ou appli</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9885,7 +9889,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>S17_5_ALERTE</t>
+          <t>S18_1_ALERTE</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -9913,7 +9917,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>S17_5_COM</t>
+          <t>S18_1_COM</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -9941,7 +9945,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>S18_1</t>
+          <t>S18_2</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -9951,7 +9955,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S18_1 Connaissance des canaux — Le conseiller a-t-il démontré une bonne connaissance des procédures via USSD et/ou appli</t>
+          <t>S18_2 Explication pas-à-pas — Le conseiller a-t-il expliqué la procédure de manière claire et détaillée, étape par étape</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9973,7 +9977,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>S18_1_ALERTE</t>
+          <t>S18_2_ALERTE</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -10001,7 +10005,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>S18_1_COM</t>
+          <t>S18_2_COM</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -10029,7 +10033,7 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>S18_2</t>
+          <t>S18_3</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -10039,7 +10043,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>S18_2 Explication pas-à-pas — Le conseiller a-t-il expliqué la procédure de manière claire et détaillée, étape par étape</t>
+          <t>S18_3 Frais et conditions — Le conseiller a-t-il informé le client des éventuels frais ou conditions applicables au tran</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10061,7 +10065,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>S18_2_ALERTE</t>
+          <t>S18_3_ALERTE</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -10089,7 +10093,7 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>S18_2_COM</t>
+          <t>S18_3_COM</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -10117,7 +10121,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>S18_3</t>
+          <t>S19_1</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -10127,7 +10131,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>S18_3 Frais et conditions — Le conseiller a-t-il informé le client des éventuels frais ou conditions applicables au tran</t>
+          <t>S19_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause probable du problème (délai technique, erreur de n</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10149,7 +10153,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>S18_3_ALERTE</t>
+          <t>S19_1_ALERTE</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -10177,7 +10181,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>S18_3_COM</t>
+          <t>S19_1_COM</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -10205,7 +10209,7 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>S19_1</t>
+          <t>S19_2</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -10215,7 +10219,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>S19_1 Diagnostic — Le conseiller a-t-il cherché à identifier la cause probable du problème (délai technique, erreur de n</t>
+          <t>S19_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité et de vérification d'identité propres au Mobil</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10237,7 +10241,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>S19_1_ALERTE</t>
+          <t>S19_2_ALERTE</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -10265,7 +10269,7 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>S19_1_COM</t>
+          <t>S19_2_COM</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -10293,7 +10297,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>S19_2</t>
+          <t>S19_3</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -10303,7 +10307,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>S19_2 Sécurité — Le conseiller a-t-il respecté les procédures de sécurité et de vérification d'identité propres au Mobil</t>
+          <t>S19_3 Traçabilité — Le conseiller a-t-il vérifié la transaction à l'aide des références fournies par le client ?</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -10325,7 +10329,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>S19_2_ALERTE</t>
+          <t>S19_3_ALERTE</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -10353,7 +10357,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>S19_2_COM</t>
+          <t>S19_3_COM</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -10381,7 +10385,7 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>S19_3</t>
+          <t>S19_4</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -10391,7 +10395,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S19_3 Traçabilité — Le conseiller a-t-il vérifié la transaction à l'aide des références fournies par le client ?</t>
+          <t>S19_4 Procédure de réclamation et délai — Le conseiller a-t-il expliqué la procédure de réclamation et communiqué un dél</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10413,7 +10417,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>S19_3_ALERTE</t>
+          <t>S19_4_ALERTE</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -10441,7 +10445,7 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>S19_3_COM</t>
+          <t>S19_4_COM</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -10469,7 +10473,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>S19_4</t>
+          <t>S20_1</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -10479,7 +10483,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>S19_4 Procédure de réclamation et délai — Le conseiller a-t-il expliqué la procédure de réclamation et communiqué un dél</t>
+          <t>S20_1 Maîtrise de la procédure — Le conseiller a-t-il connu et expliqué correctement la procédure applicable à ce type d</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -10501,7 +10505,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>S19_4_ALERTE</t>
+          <t>S20_1_ALERTE</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -10529,7 +10533,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>S19_4_COM</t>
+          <t>S20_1_COM</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -10557,7 +10561,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>S20_1</t>
+          <t>S20_2</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -10567,7 +10571,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>S20_1 Maîtrise de la procédure — Le conseiller a-t-il connu et expliqué correctement la procédure applicable à ce type d</t>
+          <t>S20_2 Gestion du risque — Le conseiller a-t-il agi avec la prudence nécessaire compte tenu de la sensibilité de l'opérat</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -10589,7 +10593,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>S20_1_ALERTE</t>
+          <t>S20_2_ALERTE</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -10617,7 +10621,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>S20_1_COM</t>
+          <t>S20_2_COM</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -10645,7 +10649,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>S20_2</t>
+          <t>S20_3</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -10655,7 +10659,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>S20_2 Gestion du risque — Le conseiller a-t-il agi avec la prudence nécessaire compte tenu de la sensibilité de l'opérat</t>
+          <t>S20_3 Transparence — Le conseiller a-t-il été transparent sur les possibilités réelles d'annulation ou de récupération d</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -10677,7 +10681,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>S20_2_ALERTE</t>
+          <t>S20_3_ALERTE</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -10705,7 +10709,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>S20_2_COM</t>
+          <t>S20_3_COM</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -10733,7 +10737,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>S20_3</t>
+          <t>S20_4</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -10743,7 +10747,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>S20_3 Transparence — Le conseiller a-t-il été transparent sur les possibilités réelles d'annulation ou de récupération d</t>
+          <t>S20_4 Accompagnement — Le conseiller a-t-il guidé le client sur les démarches à suivre (délai, pièces, contact du bénéfi</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -10765,7 +10769,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>S20_3_ALERTE</t>
+          <t>S20_4_ALERTE</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -10793,7 +10797,7 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>S20_3_COM</t>
+          <t>S20_4_COM</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -10821,7 +10825,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>S20_4</t>
+          <t>S21_1</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -10831,7 +10835,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>S20_4 Accompagnement — Le conseiller a-t-il guidé le client sur les démarches à suivre (délai, pièces, contact du bénéfi</t>
+          <t>S21_1 Maîtrise des règles de cycle de vie — Le conseiller a-t-il expliqué correctement les règles de désactivation et de</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10853,7 +10857,7 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>S20_4_ALERTE</t>
+          <t>S21_1_ALERTE</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -10881,7 +10885,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>S20_4_COM</t>
+          <t>S21_1_COM</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -10909,7 +10913,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>S21_1</t>
+          <t>S21_2</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -10919,7 +10923,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>S21_1 Maîtrise des règles de cycle de vie — Le conseiller a-t-il expliqué correctement les règles de désactivation et de</t>
+          <t>S21_2 Vérification de la disponibilité — Le conseiller a-t-il vérifié si le numéro était encore disponible pour une réac</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10941,7 +10945,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>S21_1_ALERTE</t>
+          <t>S21_2_ALERTE</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -10969,7 +10973,7 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>S21_1_COM</t>
+          <t>S21_2_COM</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -10997,7 +11001,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>S21_2</t>
+          <t>S21_3</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -11007,7 +11011,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>S21_2 Vérification de la disponibilité — Le conseiller a-t-il vérifié si le numéro était encore disponible pour une réac</t>
+          <t>S21_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives et le canal à utiliser pour la démarche ?</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -11029,7 +11033,7 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>S21_2_ALERTE</t>
+          <t>S21_3_ALERTE</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -11057,7 +11061,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>S21_2_COM</t>
+          <t>S21_3_COM</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -11085,7 +11089,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>S21_3</t>
+          <t>S21_4</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -11095,7 +11099,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>S21_3 Pièces et canal — Le conseiller a-t-il précisé les pièces justificatives et le canal à utiliser pour la démarche ?</t>
+          <t>S21_4 Alternatives — Le conseiller a-t-il proposé une alternative si le numéro n'était plus récupérable ?</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -11117,7 +11121,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>S21_3_ALERTE</t>
+          <t>S21_4_ALERTE</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -11145,7 +11149,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>S21_3_COM</t>
+          <t>S21_4_COM</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -11173,7 +11177,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>S21_4</t>
+          <t>S22_1</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -11183,7 +11187,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>S21_4 Alternatives — Le conseiller a-t-il proposé une alternative si le numéro n'était plus récupérable ?</t>
+          <t>S22_1 Vérification d'incident — Le conseiller a-t-il vérifié l'existence d'un incident réseau connu dans la zone concern</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -11205,7 +11209,7 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>S21_4_ALERTE</t>
+          <t>S22_1_ALERTE</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -11233,7 +11237,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>S21_4_COM</t>
+          <t>S22_1_COM</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -11261,7 +11265,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>S22_1</t>
+          <t>S22_2</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -11271,7 +11275,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>S22_1 Vérification d'incident — Le conseiller a-t-il vérifié l'existence d'un incident réseau connu dans la zone concern</t>
+          <t>S22_2 Collecte de la localisation — Le conseiller a-t-il précisément recueilli la localisation du client (quartier, vill</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -11293,7 +11297,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>S22_1_ALERTE</t>
+          <t>S22_2_ALERTE</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -11321,7 +11325,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>S22_1_COM</t>
+          <t>S22_2_COM</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -11349,7 +11353,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>S22_2</t>
+          <t>S22_3</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -11359,7 +11363,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>S22_2 Collecte de la localisation — Le conseiller a-t-il précisément recueilli la localisation du client (quartier, vill</t>
+          <t>S22_3 Communication proactive — Le conseiller a-t-il communiqué de façon proactive sur l'état de la situation ?</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -11381,7 +11385,7 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>S22_2_ALERTE</t>
+          <t>S22_3_ALERTE</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -11409,7 +11413,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>S22_2_COM</t>
+          <t>S22_3_COM</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -11437,7 +11441,7 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>S22_3</t>
+          <t>S22_4</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -11447,7 +11451,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>S22_3 Communication proactive — Le conseiller a-t-il communiqué de façon proactive sur l'état de la situation ?</t>
+          <t>S22_4 Délai / next step — Le conseiller a-t-il donné un délai ou une prochaine étape claire au client ?</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -11469,7 +11473,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>S22_3_ALERTE</t>
+          <t>S22_4_ALERTE</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -11497,7 +11501,7 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>S22_3_COM</t>
+          <t>S22_4_COM</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -11525,7 +11529,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>S22_4</t>
+          <t>S23_1</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -11535,7 +11539,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>S22_4 Délai / next step — Le conseiller a-t-il donné un délai ou une prochaine étape claire au client ?</t>
+          <t>S23_1 Capacité d'adaptation — Le conseiller a-t-il su adapter sa reformulation à la demande du client ?</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -11557,7 +11561,7 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>S22_4_ALERTE</t>
+          <t>S23_1_ALERTE</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -11585,7 +11589,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>S22_4_COM</t>
+          <t>S23_1_COM</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -11613,7 +11617,7 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>S23_1</t>
+          <t>S23_2</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -11623,7 +11627,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>S23_1 Capacité d'adaptation — Le conseiller a-t-il su adapter sa reformulation à la demande du client ?</t>
+          <t>S23_2 Patience — Le conseiller a-t-il fait preuve de patience face à la demande de réexplication ?</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -11645,7 +11649,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>S23_1_ALERTE</t>
+          <t>S23_2_ALERTE</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -11673,7 +11677,7 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>S23_1_COM</t>
+          <t>S23_2_COM</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -11701,7 +11705,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>S23_2</t>
+          <t>S23_3</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -11711,7 +11715,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>S23_2 Patience — Le conseiller a-t-il fait preuve de patience face à la demande de réexplication ?</t>
+          <t>S23_3 Langage simple — Le conseiller a-t-il reformulé son explication avec des mots simples, sans jargon technique ?</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -11733,7 +11737,7 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>S23_2_ALERTE</t>
+          <t>S23_3_ALERTE</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -11761,7 +11765,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>S23_2_COM</t>
+          <t>S23_3_COM</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -11789,7 +11793,7 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>S23_3</t>
+          <t>S23_4</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -11799,7 +11803,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>S23_3 Langage simple — Le conseiller a-t-il reformulé son explication avec des mots simples, sans jargon technique ?</t>
+          <t>S23_4 Vérification de compréhension — Le conseiller a-t-il vérifié, à la fin de son explication, que le client avait bie</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -11821,7 +11825,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>S23_3_ALERTE</t>
+          <t>S23_4_ALERTE</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -11849,7 +11853,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>S23_3_COM</t>
+          <t>S23_4_COM</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -11877,7 +11881,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>S23_4</t>
+          <t>S24_1</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -11887,7 +11891,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>S23_4 Vérification de compréhension — Le conseiller a-t-il vérifié, à la fin de son explication, que le client avait bie</t>
+          <t>S24_1 Inclusion — Le conseiller a-t-il adapté son discours et son rythme au niveau d'aisance digitale du client ?</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11909,7 +11913,7 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>S23_4_ALERTE</t>
+          <t>S24_1_ALERTE</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -11937,7 +11941,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>S23_4_COM</t>
+          <t>S24_1_COM</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -11965,7 +11969,7 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>S24_1</t>
+          <t>S24_2</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -11975,7 +11979,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>S24_1 Inclusion — Le conseiller a-t-il adapté son discours et son rythme au niveau d'aisance digitale du client ?</t>
+          <t>S24_2 Patience — Le conseiller a-t-il fait preuve de patience tout au long de l'accompagnement ?</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11997,7 +12001,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>S24_1_ALERTE</t>
+          <t>S24_2_ALERTE</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -12025,7 +12029,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>S24_1_COM</t>
+          <t>S24_2_COM</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -12053,7 +12057,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>S24_2</t>
+          <t>S24_3</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -12063,7 +12067,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>S24_2 Patience — Le conseiller a-t-il fait preuve de patience tout au long de l'accompagnement ?</t>
+          <t>S24_3 Guidage étape par étape — Le conseiller a-t-il guidé le client pas à pas dans la réalisation de l'opération ?</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -12085,7 +12089,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>S24_2_ALERTE</t>
+          <t>S24_3_ALERTE</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -12113,7 +12117,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>S24_2_COM</t>
+          <t>S24_3_COM</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -12141,7 +12145,7 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>S24_3</t>
+          <t>S24_4</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -12151,7 +12155,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>S24_3 Guidage étape par étape — Le conseiller a-t-il guidé le client pas à pas dans la réalisation de l'opération ?</t>
+          <t>S24_4 Alternative non digitale — Le conseiller a-t-il proposé, si utile, une alternative non digitale (USSD, agence) ?</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -12173,7 +12177,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>S24_3_ALERTE</t>
+          <t>S24_4_ALERTE</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -12201,7 +12205,7 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>S24_3_COM</t>
+          <t>S24_4_COM</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -12229,7 +12233,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>S24_4</t>
+          <t>S25_1</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -12239,7 +12243,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>S24_4 Alternative non digitale — Le conseiller a-t-il proposé, si utile, une alternative non digitale (USSD, agence) ?</t>
+          <t>S25_1 Ownership — Le conseiller a-t-il pris la demande en charge sans se défausser immédiatement ?</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -12261,7 +12265,7 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>S24_4_ALERTE</t>
+          <t>S25_1_ALERTE</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -12289,7 +12293,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>S24_4_COM</t>
+          <t>S25_1_COM</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -12317,7 +12321,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>S25_1</t>
+          <t>S25_2</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -12327,7 +12331,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>S25_1 Ownership — Le conseiller a-t-il pris la demande en charge sans se défausser immédiatement ?</t>
+          <t>S25_2 Capacité d'orientation — Le conseiller a-t-il su orienter le client vers le bon service ou canal de traitement ?</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -12349,7 +12353,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>S25_1_ALERTE</t>
+          <t>S25_2_ALERTE</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -12377,7 +12381,7 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>S25_1_COM</t>
+          <t>S25_2_COM</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -12405,7 +12409,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>S25_2</t>
+          <t>S25_3</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -12415,7 +12419,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>S25_2 Capacité d'orientation — Le conseiller a-t-il su orienter le client vers le bon service ou canal de traitement ?</t>
+          <t>S25_3 Enregistrement de la plainte — Le conseiller a-t-il procédé ou proposé l'enregistrement formel de la réclamation ?</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -12437,7 +12441,7 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>S25_2_ALERTE</t>
+          <t>S25_3_ALERTE</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -12465,7 +12469,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>S25_2_COM</t>
+          <t>S25_3_COM</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -12493,7 +12497,7 @@
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>S25_3</t>
+          <t>S25_4</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -12503,7 +12507,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>S25_3 Enregistrement de la plainte — Le conseiller a-t-il procédé ou proposé l'enregistrement formel de la réclamation ?</t>
+          <t>S25_4 Absence de renvoi abusif — Le conseiller a-t-il évité tout renvoi injustifié ou toute fin de non-recevoir ?</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -12525,7 +12529,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>S25_3_ALERTE</t>
+          <t>S25_4_ALERTE</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -12553,7 +12557,7 @@
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>S25_3_COM</t>
+          <t>S25_4_COM</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -12581,7 +12585,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>S25_4</t>
+          <t>SCORE_I</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -12591,19 +12595,15 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>S25_4 Absence de renvoi abusif — Le conseiller a-t-il évité tout renvoi injustifié ou toute fin de non-recevoir ?</t>
+          <t>Score — Maîtrise du scénario</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>select_one conformite</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>section I</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
           <t>I. MAÎTRISE DU SCÉNARIO</t>
@@ -12613,7 +12613,7 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>S25_4_ALERTE</t>
+          <t>Q24</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -12623,25 +12623,25 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Non conforme — quel cas d'alerte critique ce constat révèle-t-il ?</t>
+          <t>Q24 Quel est le principal point fort de cet appel ?</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>select_multiple alertes_nc</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>I. MAÎTRISE DU SCÉNARIO</t>
+          <t>Synthèse qualitative</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>S25_4_COM</t>
+          <t>Q25</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Non conforme — décrivez le fait observé ou rapportez la formulation exacte du conseiller.</t>
+          <t>Q25 Quel est le principal irritant ou effort subi par le client ?</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -12662,14 +12662,14 @@
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>I. MAÎTRISE DU SCÉNARIO</t>
+          <t>Synthèse qualitative</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>SCORE_I</t>
+          <t>Q26</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -12679,25 +12679,25 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Score — Maîtrise du scénario</t>
+          <t>Q26 Le client devrait-il rappeler ou contacter un autre canal pour le même motif ?</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one oui_non</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>I. MAÎTRISE DU SCÉNARIO</t>
+          <t>Synthèse qualitative</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q26_TXT</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Q24 Quel est le principal point fort de cet appel ?</t>
+          <t>Q26 Pourquoi ?</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -12723,37 +12723,37 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="inlineStr">
-        <is>
-          <t>Q25</t>
-        </is>
-      </c>
-      <c r="B421" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>HEURE_FIN</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>table MDS JOB 001/26</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Q25 Quel est le principal irritant ou effort subi par le client ?</t>
+          <t>Heure fin</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Synthèse qualitative</t>
+          <t>Fin de l'évaluation</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>SCORE_TOTAL</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -12763,100 +12763,16 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Q26 Le client devrait-il rappeler ou contacter un autre canal pour le même motif ?</t>
+          <t>Score total de l'appel</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>select_one oui_non</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
-        <is>
-          <t>Synthèse qualitative</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="2" t="inlineStr">
-        <is>
-          <t>Q26_TXT</t>
-        </is>
-      </c>
-      <c r="B423" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>Q26 Pourquoi ?</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>Synthèse qualitative</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>HEURE_FIN</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>table MDS JOB 001/26</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>Heure fin</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>Fin de l'évaluation</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="2" t="inlineStr">
-        <is>
-          <t>SCORE_TOTAL</t>
-        </is>
-      </c>
-      <c r="B425" s="2" t="inlineStr">
-        <is>
-          <t>déduit — à valider</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>Score total de l'appel</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr">
         <is>
           <t>Fin de l'évaluation</t>
         </is>
